--- a/forms/contact/person-edit.xlsx
+++ b/forms/contact/person-edit.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree\forms\contact\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId5"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="116">
   <si>
     <t>list_name</t>
   </si>
@@ -286,9 +294,6 @@
     <t>numbers</t>
   </si>
   <si>
-    <t>regex(.,'^0[0-9]{9}$')</t>
-  </si>
-  <si>
     <t>Use the following format 0XXXXXXXXX</t>
   </si>
   <si>
@@ -378,50 +383,60 @@
   <si>
     <t>../../../inputs/user/facility_id</t>
   </si>
+  <si>
+    <t>tel</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="10">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF833C0B"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -431,7 +446,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -447,17 +462,26 @@
     </fill>
   </fills>
   <borders count="5">
-    <border/>
     <border>
       <left/>
+      <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -472,6 +496,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -484,163 +509,400 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="33">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="none"/>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB1005"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.14"/>
-    <col customWidth="1" min="2" max="2" width="48.14"/>
-    <col customWidth="1" min="3" max="3" width="27.86"/>
-    <col customWidth="1" min="4" max="4" width="28.71"/>
-    <col customWidth="1" min="5" max="5" width="15.57"/>
-    <col customWidth="1" min="6" max="6" width="14.57"/>
-    <col customWidth="1" min="7" max="7" width="19.57"/>
-    <col customWidth="1" min="8" max="8" width="10.71"/>
-    <col customWidth="1" min="9" max="9" width="24.14"/>
-    <col customWidth="1" min="10" max="10" width="132.71"/>
-    <col customWidth="1" min="11" max="11" width="36.29"/>
-    <col customWidth="1" min="12" max="12" width="36.71"/>
-    <col customWidth="1" min="13" max="13" width="12.43"/>
-    <col customWidth="1" min="14" max="14" width="19.71"/>
-    <col customWidth="1" min="15" max="15" width="12.86"/>
-    <col customWidth="1" min="16" max="28" width="8.71"/>
+    <col min="1" max="1" width="24.1328125" customWidth="1"/>
+    <col min="2" max="2" width="48.1328125" customWidth="1"/>
+    <col min="3" max="3" width="27.86328125" customWidth="1"/>
+    <col min="4" max="4" width="28.6796875" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.6796875" customWidth="1"/>
+    <col min="9" max="9" width="24.1328125" customWidth="1"/>
+    <col min="10" max="10" width="132.6796875" customWidth="1"/>
+    <col min="11" max="11" width="36.26953125" customWidth="1"/>
+    <col min="12" max="12" width="36.6796875" customWidth="1"/>
+    <col min="13" max="13" width="12.40625" customWidth="1"/>
+    <col min="14" max="14" width="19.6796875" customWidth="1"/>
+    <col min="15" max="15" width="12.86328125" customWidth="1"/>
+    <col min="16" max="28" width="8.6796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:28" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -702,7 +964,7 @@
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:28" ht="14.25" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>25</v>
       </c>
@@ -717,7 +979,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -742,7 +1004,7 @@
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:28" ht="14.25" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>25</v>
       </c>
@@ -780,7 +1042,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:28" ht="14.25" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
@@ -818,7 +1080,7 @@
       <c r="AA4" s="15"/>
       <c r="AB4" s="15"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:28" ht="14.25" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>36</v>
       </c>
@@ -856,7 +1118,7 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:28" ht="14.25" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>36</v>
       </c>
@@ -894,7 +1156,7 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:28" ht="14.25" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>46</v>
       </c>
@@ -928,7 +1190,7 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:28" ht="14.25" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>46</v>
       </c>
@@ -962,7 +1224,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:28" ht="14.25" customHeight="1">
       <c r="A9" s="19" t="s">
         <v>47</v>
       </c>
@@ -1000,7 +1262,7 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:28" ht="14.25" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>51</v>
       </c>
@@ -1038,7 +1300,7 @@
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:28" ht="14.25" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>55</v>
       </c>
@@ -1072,7 +1334,7 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:28" ht="14.25" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>25</v>
       </c>
@@ -1112,7 +1374,7 @@
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:28" ht="14.25" customHeight="1">
       <c r="A13" s="24" t="s">
         <v>60</v>
       </c>
@@ -1152,7 +1414,7 @@
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:28" ht="14.25" customHeight="1">
       <c r="A14" s="24" t="s">
         <v>60</v>
       </c>
@@ -1194,7 +1456,7 @@
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:28" ht="14.25" customHeight="1">
       <c r="A15" s="24" t="s">
         <v>63</v>
       </c>
@@ -1234,7 +1496,7 @@
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:28" ht="14.25" customHeight="1">
       <c r="A16" s="24" t="s">
         <v>63</v>
       </c>
@@ -1274,7 +1536,7 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:28" ht="14.25" customHeight="1">
       <c r="A17" s="24" t="s">
         <v>63</v>
       </c>
@@ -1314,7 +1576,7 @@
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:28" ht="14.25" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>63</v>
       </c>
@@ -1354,7 +1616,7 @@
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:28" ht="14.25" customHeight="1">
       <c r="A19" s="24" t="s">
         <v>74</v>
       </c>
@@ -1396,9 +1658,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:28" ht="14.25" customHeight="1">
       <c r="A20" s="24" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>80</v>
@@ -1419,14 +1681,14 @@
         <v>84</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="J20" s="28" t="s">
+      <c r="K20" s="28" t="s">
         <v>86</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>87</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="3"/>
@@ -1448,18 +1710,18 @@
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:28" ht="14.25" customHeight="1">
       <c r="A21" s="24" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="B21" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="9" t="s">
@@ -1469,14 +1731,14 @@
         <v>84</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="J21" s="28" t="s">
+      <c r="K21" s="28" t="s">
         <v>86</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>87</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="3"/>
@@ -1496,25 +1758,25 @@
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:28" ht="14.25" customHeight="1">
       <c r="A22" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="C22" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>62</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -1538,12 +1800,12 @@
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:28" ht="14.25" customHeight="1">
       <c r="A23" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="29" t="s">
         <v>96</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>97</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="29"/>
@@ -1555,7 +1817,7 @@
       <c r="J23" s="30"/>
       <c r="K23" s="30"/>
       <c r="L23" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M23" s="30"/>
       <c r="N23" s="30"/>
@@ -1574,12 +1836,12 @@
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:28" ht="14.25" customHeight="1">
       <c r="A24" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C24" s="29"/>
       <c r="D24" s="29"/>
@@ -1591,7 +1853,7 @@
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
       <c r="L24" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M24" s="30"/>
       <c r="N24" s="30"/>
@@ -1610,12 +1872,12 @@
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:28" ht="14.25" customHeight="1">
       <c r="A25" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -1627,7 +1889,7 @@
       <c r="J25" s="30"/>
       <c r="K25" s="30"/>
       <c r="L25" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M25" s="30"/>
       <c r="N25" s="30"/>
@@ -1646,9 +1908,9 @@
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:28" ht="14.25" customHeight="1">
       <c r="A26" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>3</v>
@@ -1663,7 +1925,7 @@
       <c r="J26" s="30"/>
       <c r="K26" s="30"/>
       <c r="L26" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M26" s="30"/>
       <c r="N26" s="30"/>
@@ -1682,12 +1944,12 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:28" ht="14.25" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="10"/>
@@ -1699,16 +1961,16 @@
       <c r="J27" s="26"/>
       <c r="K27" s="15"/>
       <c r="L27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O27" s="15"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:28" ht="14.25" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>30</v>
@@ -1728,12 +1990,12 @@
       <c r="L28" s="15"/>
       <c r="O28" s="16"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:28" ht="14.25" customHeight="1">
       <c r="A29" s="24" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>30</v>
@@ -1768,12 +2030,12 @@
       <c r="AA29" s="15"/>
       <c r="AB29" s="15"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:28" ht="14.25" customHeight="1">
       <c r="A30" s="24" t="s">
         <v>60</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>30</v>
@@ -1808,12 +2070,12 @@
       <c r="AA30" s="15"/>
       <c r="AB30" s="15"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:28" ht="14.25" customHeight="1">
       <c r="A31" s="24" t="s">
         <v>60</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>30</v>
@@ -1848,12 +2110,12 @@
       <c r="AA31" s="15"/>
       <c r="AB31" s="15"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:28" ht="14.25" customHeight="1">
       <c r="A32" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="15"/>
@@ -1865,7 +2127,7 @@
       <c r="J32" s="13"/>
       <c r="K32" s="15"/>
       <c r="L32" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
@@ -1884,12 +2146,12 @@
       <c r="AA32" s="15"/>
       <c r="AB32" s="15"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:28" ht="14.25" customHeight="1">
       <c r="A33" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="15"/>
@@ -1901,7 +2163,7 @@
       <c r="J33" s="13"/>
       <c r="K33" s="15"/>
       <c r="L33" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
@@ -1920,12 +2182,12 @@
       <c r="AA33" s="15"/>
       <c r="AB33" s="15"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:28" ht="14.25" customHeight="1">
       <c r="A34" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="15"/>
@@ -1937,7 +2199,7 @@
       <c r="J34" s="13"/>
       <c r="K34" s="15"/>
       <c r="L34" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
@@ -1956,12 +2218,12 @@
       <c r="AA34" s="15"/>
       <c r="AB34" s="15"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:28" ht="14.25" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>46</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="15"/>
@@ -1975,7 +2237,7 @@
       <c r="L35" s="15"/>
       <c r="O35" s="16"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:28" ht="14.25" customHeight="1">
       <c r="A36" s="10" t="s">
         <v>46</v>
       </c>
@@ -1994,7 +2256,7 @@
       <c r="L36" s="15"/>
       <c r="O36" s="16"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:28" ht="14.25" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
@@ -2007,7 +2269,7 @@
       <c r="L37" s="3"/>
       <c r="O37" s="16"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:28" ht="14.25" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
@@ -2020,7 +2282,7 @@
       <c r="L38" s="3"/>
       <c r="O38" s="16"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:28" ht="14.25" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
@@ -2033,7 +2295,7 @@
       <c r="L39" s="3"/>
       <c r="O39" s="16"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:28" ht="14.25" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4"/>
@@ -2046,7 +2308,7 @@
       <c r="L40" s="3"/>
       <c r="O40" s="16"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:28" ht="14.25" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
@@ -2059,7 +2321,7 @@
       <c r="L41" s="3"/>
       <c r="O41" s="16"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="1:28" ht="14.25" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4"/>
@@ -2072,7 +2334,7 @@
       <c r="L42" s="3"/>
       <c r="O42" s="16"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:28" ht="14.25" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4"/>
@@ -2085,7 +2347,7 @@
       <c r="L43" s="3"/>
       <c r="O43" s="16"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:28" ht="14.25" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4"/>
@@ -2098,7 +2360,7 @@
       <c r="L44" s="3"/>
       <c r="O44" s="16"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:28" ht="14.25" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4"/>
@@ -2111,7 +2373,7 @@
       <c r="L45" s="3"/>
       <c r="O45" s="16"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:28" ht="14.25" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
@@ -2124,7 +2386,7 @@
       <c r="L46" s="3"/>
       <c r="O46" s="16"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:28" ht="14.25" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
@@ -2137,7 +2399,7 @@
       <c r="L47" s="3"/>
       <c r="O47" s="16"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:28" ht="14.25" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="4"/>
@@ -2150,7 +2412,7 @@
       <c r="L48" s="3"/>
       <c r="O48" s="16"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:15" ht="14.25" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="4"/>
@@ -2163,7 +2425,7 @@
       <c r="L49" s="3"/>
       <c r="O49" s="16"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:15" ht="14.25" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
@@ -2176,7 +2438,7 @@
       <c r="L50" s="3"/>
       <c r="O50" s="16"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="1:15" ht="14.25" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="4"/>
@@ -2189,7 +2451,7 @@
       <c r="L51" s="3"/>
       <c r="O51" s="16"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="1:15" ht="14.25" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="4"/>
@@ -2202,7 +2464,7 @@
       <c r="L52" s="3"/>
       <c r="O52" s="16"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="1:15" ht="14.25" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="4"/>
@@ -2215,7 +2477,7 @@
       <c r="L53" s="3"/>
       <c r="O53" s="16"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="1:15" ht="14.25" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
@@ -2228,7 +2490,7 @@
       <c r="L54" s="3"/>
       <c r="O54" s="16"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="1:15" ht="14.25" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
@@ -2241,7 +2503,7 @@
       <c r="L55" s="3"/>
       <c r="O55" s="16"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="1:15" ht="14.25" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4"/>
@@ -2254,7 +2516,7 @@
       <c r="L56" s="3"/>
       <c r="O56" s="16"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="1:15" ht="14.25" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="4"/>
@@ -2267,7 +2529,7 @@
       <c r="L57" s="3"/>
       <c r="O57" s="16"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="1:15" ht="14.25" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
@@ -2280,7 +2542,7 @@
       <c r="L58" s="3"/>
       <c r="O58" s="16"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" spans="1:15" ht="14.25" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
@@ -2293,7 +2555,7 @@
       <c r="L59" s="3"/>
       <c r="O59" s="16"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="1:15" ht="14.25" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
@@ -2306,7 +2568,7 @@
       <c r="L60" s="3"/>
       <c r="O60" s="16"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="1:15" ht="14.25" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
@@ -2319,7 +2581,7 @@
       <c r="L61" s="3"/>
       <c r="O61" s="16"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="1:15" ht="14.25" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
@@ -2332,7 +2594,7 @@
       <c r="L62" s="3"/>
       <c r="O62" s="16"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="1:15" ht="14.25" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
@@ -2345,7 +2607,7 @@
       <c r="L63" s="3"/>
       <c r="O63" s="16"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="1:15" ht="14.25" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
@@ -2358,7 +2620,7 @@
       <c r="L64" s="3"/>
       <c r="O64" s="16"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="1:15" ht="14.25" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="4"/>
@@ -2371,7 +2633,7 @@
       <c r="L65" s="3"/>
       <c r="O65" s="16"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" spans="1:15" ht="14.25" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
@@ -2384,7 +2646,7 @@
       <c r="L66" s="3"/>
       <c r="O66" s="16"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" spans="1:15" ht="14.25" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
@@ -2397,7 +2659,7 @@
       <c r="L67" s="3"/>
       <c r="O67" s="16"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="1:15" ht="14.25" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
@@ -2410,7 +2672,7 @@
       <c r="L68" s="3"/>
       <c r="O68" s="16"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="1:15" ht="14.25" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
@@ -2423,7 +2685,7 @@
       <c r="L69" s="3"/>
       <c r="O69" s="16"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" spans="1:15" ht="14.25" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
@@ -2436,7 +2698,7 @@
       <c r="L70" s="3"/>
       <c r="O70" s="16"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" spans="1:15" ht="14.25" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
@@ -2449,7 +2711,7 @@
       <c r="L71" s="3"/>
       <c r="O71" s="16"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" spans="1:15" ht="14.25" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
@@ -2462,7 +2724,7 @@
       <c r="L72" s="3"/>
       <c r="O72" s="16"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" spans="1:15" ht="14.25" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
@@ -2475,7 +2737,7 @@
       <c r="L73" s="3"/>
       <c r="O73" s="16"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" spans="1:15" ht="14.25" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
@@ -2488,7 +2750,7 @@
       <c r="L74" s="3"/>
       <c r="O74" s="16"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" spans="1:15" ht="14.25" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
@@ -2501,7 +2763,7 @@
       <c r="L75" s="3"/>
       <c r="O75" s="16"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" spans="1:15" ht="14.25" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
@@ -2514,7 +2776,7 @@
       <c r="L76" s="3"/>
       <c r="O76" s="16"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" spans="1:15" ht="14.25" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
@@ -2527,7 +2789,7 @@
       <c r="L77" s="3"/>
       <c r="O77" s="16"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" spans="1:15" ht="14.25" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
@@ -2540,7 +2802,7 @@
       <c r="L78" s="3"/>
       <c r="O78" s="16"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" spans="1:15" ht="14.25" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="4"/>
@@ -2553,7 +2815,7 @@
       <c r="L79" s="3"/>
       <c r="O79" s="16"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" spans="1:15" ht="14.25" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
@@ -2566,7 +2828,7 @@
       <c r="L80" s="3"/>
       <c r="O80" s="16"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" spans="1:15" ht="14.25" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="4"/>
@@ -2579,7 +2841,7 @@
       <c r="L81" s="3"/>
       <c r="O81" s="16"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" spans="1:15" ht="14.25" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="4"/>
@@ -2592,7 +2854,7 @@
       <c r="L82" s="3"/>
       <c r="O82" s="16"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" spans="1:15" ht="14.25" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
@@ -2605,7 +2867,7 @@
       <c r="L83" s="3"/>
       <c r="O83" s="16"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" spans="1:15" ht="14.25" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
@@ -2618,7 +2880,7 @@
       <c r="L84" s="3"/>
       <c r="O84" s="16"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" spans="1:15" ht="14.25" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
@@ -2631,7 +2893,7 @@
       <c r="L85" s="3"/>
       <c r="O85" s="16"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" spans="1:15" ht="14.25" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
@@ -2644,7 +2906,7 @@
       <c r="L86" s="3"/>
       <c r="O86" s="16"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" spans="1:15" ht="14.25" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
@@ -2657,7 +2919,7 @@
       <c r="L87" s="3"/>
       <c r="O87" s="16"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" spans="1:15" ht="14.25" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4"/>
@@ -2670,7 +2932,7 @@
       <c r="L88" s="3"/>
       <c r="O88" s="16"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" spans="1:15" ht="14.25" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
@@ -2683,7 +2945,7 @@
       <c r="L89" s="3"/>
       <c r="O89" s="16"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" spans="1:15" ht="14.25" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
@@ -2696,7 +2958,7 @@
       <c r="L90" s="3"/>
       <c r="O90" s="16"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" spans="1:15" ht="14.25" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4"/>
@@ -2709,7 +2971,7 @@
       <c r="L91" s="3"/>
       <c r="O91" s="16"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" spans="1:15" ht="14.25" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4"/>
@@ -2722,7 +2984,7 @@
       <c r="L92" s="3"/>
       <c r="O92" s="16"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" spans="1:15" ht="14.25" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="4"/>
@@ -2735,7 +2997,7 @@
       <c r="L93" s="3"/>
       <c r="O93" s="16"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" spans="1:15" ht="14.25" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="4"/>
@@ -2748,7 +3010,7 @@
       <c r="L94" s="3"/>
       <c r="O94" s="16"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" spans="1:15" ht="14.25" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="4"/>
@@ -2761,7 +3023,7 @@
       <c r="L95" s="3"/>
       <c r="O95" s="16"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" spans="1:15" ht="14.25" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="4"/>
@@ -2774,7 +3036,7 @@
       <c r="L96" s="3"/>
       <c r="O96" s="16"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" spans="1:15" ht="14.25" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="4"/>
@@ -2787,7 +3049,7 @@
       <c r="L97" s="3"/>
       <c r="O97" s="16"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="4"/>
@@ -2800,7 +3062,7 @@
       <c r="L98" s="3"/>
       <c r="O98" s="16"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" spans="1:15" ht="14.25" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="4"/>
@@ -2813,7 +3075,7 @@
       <c r="L99" s="3"/>
       <c r="O99" s="16"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" spans="1:15" ht="14.25" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4"/>
@@ -2826,7 +3088,7 @@
       <c r="L100" s="3"/>
       <c r="O100" s="16"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" spans="1:15" ht="14.25" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="4"/>
@@ -2839,7 +3101,7 @@
       <c r="L101" s="3"/>
       <c r="O101" s="16"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" spans="1:15" ht="14.25" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -2852,7 +3114,7 @@
       <c r="L102" s="3"/>
       <c r="O102" s="16"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" spans="1:15" ht="14.25" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="4"/>
@@ -2865,7 +3127,7 @@
       <c r="L103" s="3"/>
       <c r="O103" s="16"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" spans="1:15" ht="14.25" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="4"/>
@@ -2878,7 +3140,7 @@
       <c r="L104" s="3"/>
       <c r="O104" s="16"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" spans="1:15" ht="14.25" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="4"/>
@@ -2891,7 +3153,7 @@
       <c r="L105" s="3"/>
       <c r="O105" s="16"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" spans="1:15" ht="14.25" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="4"/>
@@ -2904,7 +3166,7 @@
       <c r="L106" s="3"/>
       <c r="O106" s="16"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" spans="1:15" ht="14.25" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="4"/>
@@ -2917,7 +3179,7 @@
       <c r="L107" s="3"/>
       <c r="O107" s="16"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" spans="1:15" ht="14.25" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="4"/>
@@ -2930,7 +3192,7 @@
       <c r="L108" s="3"/>
       <c r="O108" s="16"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" spans="1:15" ht="14.25" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="4"/>
@@ -2943,7 +3205,7 @@
       <c r="L109" s="3"/>
       <c r="O109" s="16"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" spans="1:15" ht="14.25" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="4"/>
@@ -2956,7 +3218,7 @@
       <c r="L110" s="3"/>
       <c r="O110" s="16"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" spans="1:15" ht="14.25" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="4"/>
@@ -2969,7 +3231,7 @@
       <c r="L111" s="3"/>
       <c r="O111" s="16"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" spans="1:15" ht="14.25" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -2982,7 +3244,7 @@
       <c r="L112" s="3"/>
       <c r="O112" s="16"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" spans="1:15" ht="14.25" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4"/>
@@ -2995,7 +3257,7 @@
       <c r="L113" s="3"/>
       <c r="O113" s="16"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" spans="1:15" ht="14.25" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4"/>
@@ -3008,7 +3270,7 @@
       <c r="L114" s="3"/>
       <c r="O114" s="16"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" spans="1:15" ht="14.25" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="4"/>
@@ -3021,7 +3283,7 @@
       <c r="L115" s="3"/>
       <c r="O115" s="16"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" spans="1:15" ht="14.25" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="4"/>
@@ -3034,7 +3296,7 @@
       <c r="L116" s="3"/>
       <c r="O116" s="16"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" spans="1:15" ht="14.25" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="4"/>
@@ -3047,7 +3309,7 @@
       <c r="L117" s="3"/>
       <c r="O117" s="16"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" spans="1:15" ht="14.25" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="4"/>
@@ -3060,7 +3322,7 @@
       <c r="L118" s="3"/>
       <c r="O118" s="16"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" spans="1:15" ht="14.25" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="4"/>
@@ -3073,7 +3335,7 @@
       <c r="L119" s="3"/>
       <c r="O119" s="16"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" spans="1:15" ht="14.25" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="4"/>
@@ -3086,7 +3348,7 @@
       <c r="L120" s="3"/>
       <c r="O120" s="16"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" spans="1:15" ht="14.25" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="4"/>
@@ -3099,7 +3361,7 @@
       <c r="L121" s="3"/>
       <c r="O121" s="16"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" spans="1:15" ht="14.25" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="4"/>
@@ -3112,7 +3374,7 @@
       <c r="L122" s="3"/>
       <c r="O122" s="16"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" spans="1:15" ht="14.25" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="4"/>
@@ -3125,7 +3387,7 @@
       <c r="L123" s="3"/>
       <c r="O123" s="16"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" spans="1:15" ht="14.25" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="4"/>
@@ -3138,7 +3400,7 @@
       <c r="L124" s="3"/>
       <c r="O124" s="16"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" spans="1:15" ht="14.25" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="4"/>
@@ -3151,7 +3413,7 @@
       <c r="L125" s="3"/>
       <c r="O125" s="16"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="1:15" ht="14.25" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="4"/>
@@ -3164,7 +3426,7 @@
       <c r="L126" s="3"/>
       <c r="O126" s="16"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="1:15" ht="14.25" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="4"/>
@@ -3177,7 +3439,7 @@
       <c r="L127" s="3"/>
       <c r="O127" s="16"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="1:15" ht="14.25" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="4"/>
@@ -3190,7 +3452,7 @@
       <c r="L128" s="3"/>
       <c r="O128" s="16"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="1:15" ht="14.25" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="4"/>
@@ -3203,7 +3465,7 @@
       <c r="L129" s="3"/>
       <c r="O129" s="16"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="1:15" ht="14.25" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="4"/>
@@ -3216,7 +3478,7 @@
       <c r="L130" s="3"/>
       <c r="O130" s="16"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" spans="1:15" ht="14.25" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="4"/>
@@ -3229,7 +3491,7 @@
       <c r="L131" s="3"/>
       <c r="O131" s="16"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="1:15" ht="14.25" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="4"/>
@@ -3242,7 +3504,7 @@
       <c r="L132" s="3"/>
       <c r="O132" s="16"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" spans="1:15" ht="14.25" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="4"/>
@@ -3255,7 +3517,7 @@
       <c r="L133" s="3"/>
       <c r="O133" s="16"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="1:15" ht="14.25" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="4"/>
@@ -3268,7 +3530,7 @@
       <c r="L134" s="3"/>
       <c r="O134" s="16"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" spans="1:15" ht="14.25" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="4"/>
@@ -3281,7 +3543,7 @@
       <c r="L135" s="3"/>
       <c r="O135" s="16"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" spans="1:15" ht="14.25" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="4"/>
@@ -3294,7 +3556,7 @@
       <c r="L136" s="3"/>
       <c r="O136" s="16"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" spans="1:15" ht="14.25" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="4"/>
@@ -3307,7 +3569,7 @@
       <c r="L137" s="3"/>
       <c r="O137" s="16"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" spans="1:15" ht="14.25" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="4"/>
@@ -3320,7 +3582,7 @@
       <c r="L138" s="3"/>
       <c r="O138" s="16"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" spans="1:15" ht="14.25" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="4"/>
@@ -3333,7 +3595,7 @@
       <c r="L139" s="3"/>
       <c r="O139" s="16"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" spans="1:15" ht="14.25" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="4"/>
@@ -3346,7 +3608,7 @@
       <c r="L140" s="3"/>
       <c r="O140" s="16"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" spans="1:15" ht="14.25" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="4"/>
@@ -3359,7 +3621,7 @@
       <c r="L141" s="3"/>
       <c r="O141" s="16"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" spans="1:15" ht="14.25" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="4"/>
@@ -3372,7 +3634,7 @@
       <c r="L142" s="3"/>
       <c r="O142" s="16"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" spans="1:15" ht="14.25" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="4"/>
@@ -3385,7 +3647,7 @@
       <c r="L143" s="3"/>
       <c r="O143" s="16"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" spans="1:15" ht="14.25" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="4"/>
@@ -3398,7 +3660,7 @@
       <c r="L144" s="3"/>
       <c r="O144" s="16"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" spans="1:15" ht="14.25" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="4"/>
@@ -3411,7 +3673,7 @@
       <c r="L145" s="3"/>
       <c r="O145" s="16"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" spans="1:15" ht="14.25" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="4"/>
@@ -3424,7 +3686,7 @@
       <c r="L146" s="3"/>
       <c r="O146" s="16"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" spans="1:15" ht="14.25" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="4"/>
@@ -3437,7 +3699,7 @@
       <c r="L147" s="3"/>
       <c r="O147" s="16"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" spans="1:15" ht="14.25" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="4"/>
@@ -3450,7 +3712,7 @@
       <c r="L148" s="3"/>
       <c r="O148" s="16"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" spans="1:15" ht="14.25" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="4"/>
@@ -3463,7 +3725,7 @@
       <c r="L149" s="3"/>
       <c r="O149" s="16"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" spans="1:15" ht="14.25" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="4"/>
@@ -3476,7 +3738,7 @@
       <c r="L150" s="3"/>
       <c r="O150" s="16"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" spans="1:15" ht="14.25" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="4"/>
@@ -3489,7 +3751,7 @@
       <c r="L151" s="3"/>
       <c r="O151" s="16"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" spans="1:15" ht="14.25" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="4"/>
@@ -3502,7 +3764,7 @@
       <c r="L152" s="3"/>
       <c r="O152" s="16"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" spans="1:15" ht="14.25" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="4"/>
@@ -3515,7 +3777,7 @@
       <c r="L153" s="3"/>
       <c r="O153" s="16"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" spans="1:15" ht="14.25" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="4"/>
@@ -3528,7 +3790,7 @@
       <c r="L154" s="3"/>
       <c r="O154" s="16"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" spans="1:15" ht="14.25" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="4"/>
@@ -3541,7 +3803,7 @@
       <c r="L155" s="3"/>
       <c r="O155" s="16"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" spans="1:15" ht="14.25" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="4"/>
@@ -3554,7 +3816,7 @@
       <c r="L156" s="3"/>
       <c r="O156" s="16"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" spans="1:15" ht="14.25" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="4"/>
@@ -3567,7 +3829,7 @@
       <c r="L157" s="3"/>
       <c r="O157" s="16"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" spans="1:15" ht="14.25" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="4"/>
@@ -3580,7 +3842,7 @@
       <c r="L158" s="3"/>
       <c r="O158" s="16"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" spans="1:15" ht="14.25" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="4"/>
@@ -3593,7 +3855,7 @@
       <c r="L159" s="3"/>
       <c r="O159" s="16"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" spans="1:15" ht="14.25" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="4"/>
@@ -3606,7 +3868,7 @@
       <c r="L160" s="3"/>
       <c r="O160" s="16"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" spans="1:15" ht="14.25" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="4"/>
@@ -3619,7 +3881,7 @@
       <c r="L161" s="3"/>
       <c r="O161" s="16"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" spans="1:15" ht="14.25" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="4"/>
@@ -3632,7 +3894,7 @@
       <c r="L162" s="3"/>
       <c r="O162" s="16"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" spans="1:15" ht="14.25" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="4"/>
@@ -3645,7 +3907,7 @@
       <c r="L163" s="3"/>
       <c r="O163" s="16"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" spans="1:15" ht="14.25" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="4"/>
@@ -3658,7 +3920,7 @@
       <c r="L164" s="3"/>
       <c r="O164" s="16"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" spans="1:15" ht="14.25" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="4"/>
@@ -3671,7 +3933,7 @@
       <c r="L165" s="3"/>
       <c r="O165" s="16"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" spans="1:15" ht="14.25" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="4"/>
@@ -3684,7 +3946,7 @@
       <c r="L166" s="3"/>
       <c r="O166" s="16"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" spans="1:15" ht="14.25" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="4"/>
@@ -3697,7 +3959,7 @@
       <c r="L167" s="3"/>
       <c r="O167" s="16"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" spans="1:15" ht="14.25" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="4"/>
@@ -3710,7 +3972,7 @@
       <c r="L168" s="3"/>
       <c r="O168" s="16"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" spans="1:15" ht="14.25" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="4"/>
@@ -3723,7 +3985,7 @@
       <c r="L169" s="3"/>
       <c r="O169" s="16"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" spans="1:15" ht="14.25" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="4"/>
@@ -3736,7 +3998,7 @@
       <c r="L170" s="3"/>
       <c r="O170" s="16"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" spans="1:15" ht="14.25" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="4"/>
@@ -3749,7 +4011,7 @@
       <c r="L171" s="3"/>
       <c r="O171" s="16"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" spans="1:15" ht="14.25" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="4"/>
@@ -3762,7 +4024,7 @@
       <c r="L172" s="3"/>
       <c r="O172" s="16"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" spans="1:15" ht="14.25" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="4"/>
@@ -3775,7 +4037,7 @@
       <c r="L173" s="3"/>
       <c r="O173" s="16"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" spans="1:15" ht="14.25" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="4"/>
@@ -3788,7 +4050,7 @@
       <c r="L174" s="3"/>
       <c r="O174" s="16"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" spans="1:15" ht="14.25" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="4"/>
@@ -3801,7 +4063,7 @@
       <c r="L175" s="3"/>
       <c r="O175" s="16"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" spans="1:15" ht="14.25" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="4"/>
@@ -3814,7 +4076,7 @@
       <c r="L176" s="3"/>
       <c r="O176" s="16"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" spans="1:15" ht="14.25" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="4"/>
@@ -3827,7 +4089,7 @@
       <c r="L177" s="3"/>
       <c r="O177" s="16"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" spans="1:15" ht="14.25" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="4"/>
@@ -3840,7 +4102,7 @@
       <c r="L178" s="3"/>
       <c r="O178" s="16"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" spans="1:15" ht="14.25" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="4"/>
@@ -3853,7 +4115,7 @@
       <c r="L179" s="3"/>
       <c r="O179" s="16"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" spans="1:15" ht="14.25" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="4"/>
@@ -3866,7 +4128,7 @@
       <c r="L180" s="3"/>
       <c r="O180" s="16"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" spans="1:15" ht="14.25" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="4"/>
@@ -3879,7 +4141,7 @@
       <c r="L181" s="3"/>
       <c r="O181" s="16"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" spans="1:15" ht="14.25" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="4"/>
@@ -3892,7 +4154,7 @@
       <c r="L182" s="3"/>
       <c r="O182" s="16"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" spans="1:15" ht="14.25" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="4"/>
@@ -3905,7 +4167,7 @@
       <c r="L183" s="3"/>
       <c r="O183" s="16"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" spans="1:15" ht="14.25" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="4"/>
@@ -3918,7 +4180,7 @@
       <c r="L184" s="3"/>
       <c r="O184" s="16"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" spans="1:15" ht="14.25" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="4"/>
@@ -3931,7 +4193,7 @@
       <c r="L185" s="3"/>
       <c r="O185" s="16"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" spans="1:15" ht="14.25" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="4"/>
@@ -3944,7 +4206,7 @@
       <c r="L186" s="3"/>
       <c r="O186" s="16"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" spans="1:15" ht="14.25" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="4"/>
@@ -3957,7 +4219,7 @@
       <c r="L187" s="3"/>
       <c r="O187" s="16"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" spans="1:15" ht="14.25" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="4"/>
@@ -3970,7 +4232,7 @@
       <c r="L188" s="3"/>
       <c r="O188" s="16"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" spans="1:15" ht="14.25" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="4"/>
@@ -3983,7 +4245,7 @@
       <c r="L189" s="3"/>
       <c r="O189" s="16"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" spans="1:15" ht="14.25" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="4"/>
@@ -3996,7 +4258,7 @@
       <c r="L190" s="3"/>
       <c r="O190" s="16"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" spans="1:15" ht="14.25" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="4"/>
@@ -4009,7 +4271,7 @@
       <c r="L191" s="3"/>
       <c r="O191" s="16"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" spans="1:15" ht="14.25" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="4"/>
@@ -4022,7 +4284,7 @@
       <c r="L192" s="3"/>
       <c r="O192" s="16"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" spans="1:15" ht="14.25" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="4"/>
@@ -4035,7 +4297,7 @@
       <c r="L193" s="3"/>
       <c r="O193" s="16"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" spans="1:15" ht="14.25" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="4"/>
@@ -4048,7 +4310,7 @@
       <c r="L194" s="3"/>
       <c r="O194" s="16"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" spans="1:15" ht="14.25" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="4"/>
@@ -4061,7 +4323,7 @@
       <c r="L195" s="3"/>
       <c r="O195" s="16"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" spans="1:15" ht="14.25" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="4"/>
@@ -4074,7 +4336,7 @@
       <c r="L196" s="3"/>
       <c r="O196" s="16"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" spans="1:15" ht="14.25" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="4"/>
@@ -4087,7 +4349,7 @@
       <c r="L197" s="3"/>
       <c r="O197" s="16"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" spans="1:15" ht="14.25" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="4"/>
@@ -4100,7 +4362,7 @@
       <c r="L198" s="3"/>
       <c r="O198" s="16"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" spans="1:15" ht="14.25" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="4"/>
@@ -4113,7 +4375,7 @@
       <c r="L199" s="3"/>
       <c r="O199" s="16"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" spans="1:15" ht="14.25" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="4"/>
@@ -4126,7 +4388,7 @@
       <c r="L200" s="3"/>
       <c r="O200" s="16"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" spans="1:15" ht="14.25" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="4"/>
@@ -4139,7 +4401,7 @@
       <c r="L201" s="3"/>
       <c r="O201" s="16"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" spans="1:15" ht="14.25" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="4"/>
@@ -4152,7 +4414,7 @@
       <c r="L202" s="3"/>
       <c r="O202" s="16"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" spans="1:15" ht="14.25" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="4"/>
@@ -4165,7 +4427,7 @@
       <c r="L203" s="3"/>
       <c r="O203" s="16"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" spans="1:15" ht="14.25" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="4"/>
@@ -4178,7 +4440,7 @@
       <c r="L204" s="3"/>
       <c r="O204" s="16"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" spans="1:15" ht="14.25" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="4"/>
@@ -4191,7 +4453,7 @@
       <c r="L205" s="3"/>
       <c r="O205" s="16"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" spans="1:15" ht="14.25" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="4"/>
@@ -4204,7 +4466,7 @@
       <c r="L206" s="3"/>
       <c r="O206" s="16"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" spans="1:15" ht="14.25" customHeight="1">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="4"/>
@@ -4217,7 +4479,7 @@
       <c r="L207" s="3"/>
       <c r="O207" s="16"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" spans="1:15" ht="14.25" customHeight="1">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="4"/>
@@ -4230,7 +4492,7 @@
       <c r="L208" s="3"/>
       <c r="O208" s="16"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" spans="1:15" ht="14.25" customHeight="1">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="4"/>
@@ -4243,7 +4505,7 @@
       <c r="L209" s="3"/>
       <c r="O209" s="16"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" spans="1:15" ht="14.25" customHeight="1">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="4"/>
@@ -4256,7 +4518,7 @@
       <c r="L210" s="3"/>
       <c r="O210" s="16"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" spans="1:15" ht="14.25" customHeight="1">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="4"/>
@@ -4269,7 +4531,7 @@
       <c r="L211" s="3"/>
       <c r="O211" s="16"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" spans="1:15" ht="14.25" customHeight="1">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="4"/>
@@ -4282,7 +4544,7 @@
       <c r="L212" s="3"/>
       <c r="O212" s="16"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" spans="1:15" ht="14.25" customHeight="1">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="4"/>
@@ -4295,7 +4557,7 @@
       <c r="L213" s="3"/>
       <c r="O213" s="16"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" spans="1:15" ht="14.25" customHeight="1">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="4"/>
@@ -4308,7 +4570,7 @@
       <c r="L214" s="3"/>
       <c r="O214" s="16"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" spans="1:15" ht="14.25" customHeight="1">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="4"/>
@@ -4321,7 +4583,7 @@
       <c r="L215" s="3"/>
       <c r="O215" s="16"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" spans="1:15" ht="14.25" customHeight="1">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="4"/>
@@ -4334,7 +4596,7 @@
       <c r="L216" s="3"/>
       <c r="O216" s="16"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" spans="1:15" ht="14.25" customHeight="1">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="4"/>
@@ -4347,7 +4609,7 @@
       <c r="L217" s="3"/>
       <c r="O217" s="16"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" spans="1:15" ht="14.25" customHeight="1">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="4"/>
@@ -4360,7 +4622,7 @@
       <c r="L218" s="3"/>
       <c r="O218" s="16"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" spans="1:15" ht="14.25" customHeight="1">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="4"/>
@@ -4373,7 +4635,7 @@
       <c r="L219" s="3"/>
       <c r="O219" s="16"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" spans="1:15" ht="14.25" customHeight="1">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="4"/>
@@ -4386,7 +4648,7 @@
       <c r="L220" s="3"/>
       <c r="O220" s="16"/>
     </row>
-    <row r="221" ht="14.25" customHeight="1">
+    <row r="221" spans="1:15" ht="14.25" customHeight="1">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="4"/>
@@ -4399,7 +4661,7 @@
       <c r="L221" s="3"/>
       <c r="O221" s="16"/>
     </row>
-    <row r="222" ht="14.25" customHeight="1">
+    <row r="222" spans="1:15" ht="14.25" customHeight="1">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="4"/>
@@ -4412,7 +4674,7 @@
       <c r="L222" s="3"/>
       <c r="O222" s="16"/>
     </row>
-    <row r="223" ht="14.25" customHeight="1">
+    <row r="223" spans="1:15" ht="14.25" customHeight="1">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="4"/>
@@ -4425,7 +4687,7 @@
       <c r="L223" s="3"/>
       <c r="O223" s="16"/>
     </row>
-    <row r="224" ht="14.25" customHeight="1">
+    <row r="224" spans="1:15" ht="14.25" customHeight="1">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="4"/>
@@ -4438,7 +4700,7 @@
       <c r="L224" s="3"/>
       <c r="O224" s="16"/>
     </row>
-    <row r="225" ht="14.25" customHeight="1">
+    <row r="225" spans="1:15" ht="14.25" customHeight="1">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="4"/>
@@ -4451,7 +4713,7 @@
       <c r="L225" s="3"/>
       <c r="O225" s="16"/>
     </row>
-    <row r="226" ht="14.25" customHeight="1">
+    <row r="226" spans="1:15" ht="14.25" customHeight="1">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="4"/>
@@ -4464,7 +4726,7 @@
       <c r="L226" s="3"/>
       <c r="O226" s="16"/>
     </row>
-    <row r="227" ht="14.25" customHeight="1">
+    <row r="227" spans="1:15" ht="14.25" customHeight="1">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="4"/>
@@ -4477,7 +4739,7 @@
       <c r="L227" s="3"/>
       <c r="O227" s="16"/>
     </row>
-    <row r="228" ht="14.25" customHeight="1">
+    <row r="228" spans="1:15" ht="14.25" customHeight="1">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="4"/>
@@ -4490,7 +4752,7 @@
       <c r="L228" s="3"/>
       <c r="O228" s="16"/>
     </row>
-    <row r="229" ht="14.25" customHeight="1">
+    <row r="229" spans="1:15" ht="14.25" customHeight="1">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="4"/>
@@ -4503,7 +4765,7 @@
       <c r="L229" s="3"/>
       <c r="O229" s="16"/>
     </row>
-    <row r="230" ht="14.25" customHeight="1">
+    <row r="230" spans="1:15" ht="14.25" customHeight="1">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="4"/>
@@ -4516,7 +4778,7 @@
       <c r="L230" s="3"/>
       <c r="O230" s="16"/>
     </row>
-    <row r="231" ht="14.25" customHeight="1">
+    <row r="231" spans="1:15" ht="14.25" customHeight="1">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="4"/>
@@ -4529,7 +4791,7 @@
       <c r="L231" s="3"/>
       <c r="O231" s="16"/>
     </row>
-    <row r="232" ht="14.25" customHeight="1">
+    <row r="232" spans="1:15" ht="14.25" customHeight="1">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="4"/>
@@ -4542,7 +4804,7 @@
       <c r="L232" s="3"/>
       <c r="O232" s="16"/>
     </row>
-    <row r="233" ht="14.25" customHeight="1">
+    <row r="233" spans="1:15" ht="14.25" customHeight="1">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="4"/>
@@ -4555,7 +4817,7 @@
       <c r="L233" s="3"/>
       <c r="O233" s="16"/>
     </row>
-    <row r="234" ht="14.25" customHeight="1">
+    <row r="234" spans="1:15" ht="14.25" customHeight="1">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="4"/>
@@ -4568,7 +4830,7 @@
       <c r="L234" s="3"/>
       <c r="O234" s="16"/>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
+    <row r="235" spans="1:15" ht="14.25" customHeight="1">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="4"/>
@@ -4581,7 +4843,7 @@
       <c r="L235" s="3"/>
       <c r="O235" s="16"/>
     </row>
-    <row r="236" ht="14.25" customHeight="1">
+    <row r="236" spans="1:15" ht="14.25" customHeight="1">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="4"/>
@@ -4594,10 +4856,10 @@
       <c r="L236" s="3"/>
       <c r="O236" s="16"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="237" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="238" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="239" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="240" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
     <row r="242" ht="15.75" customHeight="1"/>
     <row r="243" ht="15.75" customHeight="1"/>
@@ -5365,32 +5627,32 @@
     <row r="1005" ht="15.75" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A1 A15:A18 A20:A21 A27:A28 A35:A36">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A12 A14 A27:A28">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14 A29:A34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A8">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5399,29 +5661,25 @@
       <formula>"begin group"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U986"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.14"/>
-    <col customWidth="1" min="2" max="2" width="9.71"/>
-    <col customWidth="1" min="3" max="3" width="29.57"/>
-    <col customWidth="1" min="4" max="4" width="26.71"/>
-    <col customWidth="1" min="5" max="8" width="7.71"/>
-    <col customWidth="1" min="9" max="21" width="15.14"/>
+    <col min="1" max="1" width="21.1328125" customWidth="1"/>
+    <col min="2" max="2" width="9.6796875" customWidth="1"/>
+    <col min="3" max="3" width="29.54296875" customWidth="1"/>
+    <col min="4" max="4" width="26.6796875" customWidth="1"/>
+    <col min="5" max="8" width="7.6796875" customWidth="1"/>
+    <col min="9" max="21" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5452,7 +5710,7 @@
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
@@ -5483,7 +5741,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:21" ht="14.25" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -5514,7 +5772,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:21" ht="14.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="12"/>
       <c r="C4" s="14"/>
@@ -5537,7 +5795,7 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:21" ht="14.25" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="12"/>
       <c r="C5" s="14"/>
@@ -5560,7 +5818,7 @@
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:21" ht="14.25" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="12"/>
       <c r="C6" s="14"/>
@@ -5583,7 +5841,7 @@
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:21" ht="14.25" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="12"/>
       <c r="C7" s="14"/>
@@ -5606,7 +5864,7 @@
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:21" ht="14.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="12"/>
       <c r="C8" s="14"/>
@@ -5629,7 +5887,7 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="12"/>
       <c r="C9" s="3"/>
@@ -5652,7 +5910,7 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="12"/>
       <c r="C10" s="14"/>
@@ -5675,7 +5933,7 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:21" ht="14.25" customHeight="1">
       <c r="A11" s="15"/>
       <c r="B11" s="18"/>
       <c r="C11" s="20"/>
@@ -5698,7 +5956,7 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:21" ht="14.25" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="18"/>
       <c r="C12" s="20"/>
@@ -5721,7 +5979,7 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:21" ht="14.25" customHeight="1">
       <c r="A13" s="15"/>
       <c r="B13" s="18"/>
       <c r="C13" s="20"/>
@@ -5744,7 +6002,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:21" ht="14.25" customHeight="1">
       <c r="A14" s="15"/>
       <c r="B14" s="18"/>
       <c r="C14" s="20"/>
@@ -5767,7 +6025,7 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:21" ht="14.25" customHeight="1">
       <c r="A15" s="15"/>
       <c r="B15" s="18"/>
       <c r="C15" s="20"/>
@@ -5790,7 +6048,7 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:21" ht="14.25" customHeight="1">
       <c r="A16" s="15"/>
       <c r="B16" s="18"/>
       <c r="C16" s="20"/>
@@ -5813,7 +6071,7 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:21" ht="14.25" customHeight="1">
       <c r="A17" s="15"/>
       <c r="B17" s="18"/>
       <c r="C17" s="20"/>
@@ -5836,7 +6094,7 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:21" ht="14.25" customHeight="1">
       <c r="A18" s="15"/>
       <c r="B18" s="18"/>
       <c r="C18" s="20"/>
@@ -5859,7 +6117,7 @@
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:21" ht="14.25" customHeight="1">
       <c r="A19" s="15"/>
       <c r="B19" s="18"/>
       <c r="C19" s="20"/>
@@ -5882,7 +6140,7 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:21" ht="14.25" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5905,7 +6163,7 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5928,7 +6186,7 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:21" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -5951,7 +6209,7 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:21" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -5974,7 +6232,7 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:21" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -5997,7 +6255,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:21" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -6020,7 +6278,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:21" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -6043,7 +6301,7 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:21" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -6066,7 +6324,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:21" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -6089,7 +6347,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:21" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -6112,7 +6370,7 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:21" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -6135,7 +6393,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:21" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -6158,7 +6416,7 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:21" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -6181,7 +6439,7 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:21" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -6204,7 +6462,7 @@
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:21" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6227,7 +6485,7 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:21" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -6250,7 +6508,7 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:21" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -6273,7 +6531,7 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:21" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -6296,7 +6554,7 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:21" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -6319,7 +6577,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:21" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6342,7 +6600,7 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:21" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -6365,7 +6623,7 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:21" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -6388,7 +6646,7 @@
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:21" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -6411,7 +6669,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:21" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -6434,7 +6692,7 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:21" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -6457,7 +6715,7 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:21" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -6480,7 +6738,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:21" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -6503,7 +6761,7 @@
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:21" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -6526,7 +6784,7 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:21" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -6549,7 +6807,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:21" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -6572,7 +6830,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:21" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -6595,7 +6853,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:21" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -6618,7 +6876,7 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:21" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -6641,7 +6899,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:21" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -6664,7 +6922,7 @@
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:21" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -6687,7 +6945,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:21" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -6710,7 +6968,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:21" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -6733,7 +6991,7 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:21" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -6756,7 +7014,7 @@
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:21" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -6779,7 +7037,7 @@
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:21" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -6802,7 +7060,7 @@
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:21" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -6825,7 +7083,7 @@
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:21" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -6848,7 +7106,7 @@
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:21" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -6871,7 +7129,7 @@
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:21" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -6894,7 +7152,7 @@
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:21" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -6917,7 +7175,7 @@
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:21" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -6940,7 +7198,7 @@
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:21" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -6963,7 +7221,7 @@
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:21" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -6986,7 +7244,7 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:21" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -7009,7 +7267,7 @@
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:21" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -7032,7 +7290,7 @@
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:21" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -7055,7 +7313,7 @@
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:21" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -7078,7 +7336,7 @@
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:21" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -7101,7 +7359,7 @@
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:21" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -7124,7 +7382,7 @@
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:21" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -7147,7 +7405,7 @@
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:21" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -7170,7 +7428,7 @@
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:21" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -7193,7 +7451,7 @@
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:21" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -7216,7 +7474,7 @@
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:21" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -7239,7 +7497,7 @@
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:21" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -7262,7 +7520,7 @@
       <c r="T79" s="3"/>
       <c r="U79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:21" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -7285,7 +7543,7 @@
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:21" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -7308,7 +7566,7 @@
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:21" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -7331,7 +7589,7 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:21" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -7354,7 +7612,7 @@
       <c r="T83" s="3"/>
       <c r="U83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:21" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -7377,7 +7635,7 @@
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:21" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -7400,7 +7658,7 @@
       <c r="T85" s="3"/>
       <c r="U85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:21" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -7423,7 +7681,7 @@
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:21" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -7446,7 +7704,7 @@
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:21" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -7469,7 +7727,7 @@
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:21" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -7492,7 +7750,7 @@
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:21" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -7515,7 +7773,7 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:21" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -7538,7 +7796,7 @@
       <c r="T91" s="3"/>
       <c r="U91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:21" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -7561,7 +7819,7 @@
       <c r="T92" s="3"/>
       <c r="U92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:21" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -7584,7 +7842,7 @@
       <c r="T93" s="3"/>
       <c r="U93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:21" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -7607,7 +7865,7 @@
       <c r="T94" s="3"/>
       <c r="U94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:21" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -7630,7 +7888,7 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:21" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -7653,7 +7911,7 @@
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:21" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -7676,7 +7934,7 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:21" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -7699,7 +7957,7 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:21" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -7722,7 +7980,7 @@
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:21" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -7745,7 +8003,7 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:21" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -7768,7 +8026,7 @@
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:21" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -7791,7 +8049,7 @@
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:21" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -7814,7 +8072,7 @@
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:21" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -7837,7 +8095,7 @@
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:21" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -7860,7 +8118,7 @@
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:21" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -7883,7 +8141,7 @@
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:21" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -7906,7 +8164,7 @@
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:21" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -7929,7 +8187,7 @@
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:21" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -7952,7 +8210,7 @@
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:21" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -7975,7 +8233,7 @@
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:21" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -7998,7 +8256,7 @@
       <c r="T111" s="3"/>
       <c r="U111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:21" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -8021,7 +8279,7 @@
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:21" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -8044,7 +8302,7 @@
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:21" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -8067,7 +8325,7 @@
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:21" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -8090,7 +8348,7 @@
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:21" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -8113,7 +8371,7 @@
       <c r="T116" s="3"/>
       <c r="U116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:21" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -8136,7 +8394,7 @@
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:21" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -8159,7 +8417,7 @@
       <c r="T118" s="3"/>
       <c r="U118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:21" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -8182,7 +8440,7 @@
       <c r="T119" s="3"/>
       <c r="U119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:21" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -8205,7 +8463,7 @@
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:21" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -8228,7 +8486,7 @@
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:21" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -8251,7 +8509,7 @@
       <c r="T122" s="3"/>
       <c r="U122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:21" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -8274,7 +8532,7 @@
       <c r="T123" s="3"/>
       <c r="U123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:21" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -8297,7 +8555,7 @@
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:21" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -8320,7 +8578,7 @@
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:21" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -8343,7 +8601,7 @@
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:21" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -8366,7 +8624,7 @@
       <c r="T127" s="3"/>
       <c r="U127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:21" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -8389,7 +8647,7 @@
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:21" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -8412,7 +8670,7 @@
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:21" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -8435,7 +8693,7 @@
       <c r="T130" s="3"/>
       <c r="U130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:21" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -8458,7 +8716,7 @@
       <c r="T131" s="3"/>
       <c r="U131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:21" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -8481,7 +8739,7 @@
       <c r="T132" s="3"/>
       <c r="U132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:21" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -8504,7 +8762,7 @@
       <c r="T133" s="3"/>
       <c r="U133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:21" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -8527,7 +8785,7 @@
       <c r="T134" s="3"/>
       <c r="U134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:21" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -8550,7 +8808,7 @@
       <c r="T135" s="3"/>
       <c r="U135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:21" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -8573,7 +8831,7 @@
       <c r="T136" s="3"/>
       <c r="U136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:21" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -8596,7 +8854,7 @@
       <c r="T137" s="3"/>
       <c r="U137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:21" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -8619,7 +8877,7 @@
       <c r="T138" s="3"/>
       <c r="U138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:21" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -8642,7 +8900,7 @@
       <c r="T139" s="3"/>
       <c r="U139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:21" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -8665,7 +8923,7 @@
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:21" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -8688,7 +8946,7 @@
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:21" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -8711,7 +8969,7 @@
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:21" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -8734,7 +8992,7 @@
       <c r="T143" s="3"/>
       <c r="U143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:21" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -8757,7 +9015,7 @@
       <c r="T144" s="3"/>
       <c r="U144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:21" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -8780,7 +9038,7 @@
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:21" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -8803,7 +9061,7 @@
       <c r="T146" s="3"/>
       <c r="U146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:21" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -8826,7 +9084,7 @@
       <c r="T147" s="3"/>
       <c r="U147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:21" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -8849,7 +9107,7 @@
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:21" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -8872,7 +9130,7 @@
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:21" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -8895,7 +9153,7 @@
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:21" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -8918,7 +9176,7 @@
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:21" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -8941,7 +9199,7 @@
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:21" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -8964,7 +9222,7 @@
       <c r="T153" s="3"/>
       <c r="U153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:21" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -8987,7 +9245,7 @@
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:21" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -9010,7 +9268,7 @@
       <c r="T155" s="3"/>
       <c r="U155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:21" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -9033,7 +9291,7 @@
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:21" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -9056,7 +9314,7 @@
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:21" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -9079,7 +9337,7 @@
       <c r="T158" s="3"/>
       <c r="U158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:21" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -9102,7 +9360,7 @@
       <c r="T159" s="3"/>
       <c r="U159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:21" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -9125,7 +9383,7 @@
       <c r="T160" s="3"/>
       <c r="U160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:21" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -9148,7 +9406,7 @@
       <c r="T161" s="3"/>
       <c r="U161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:21" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -9171,7 +9429,7 @@
       <c r="T162" s="3"/>
       <c r="U162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:21" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -9194,7 +9452,7 @@
       <c r="T163" s="3"/>
       <c r="U163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:21" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -9217,7 +9475,7 @@
       <c r="T164" s="3"/>
       <c r="U164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:21" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -9240,7 +9498,7 @@
       <c r="T165" s="3"/>
       <c r="U165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:21" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -9263,7 +9521,7 @@
       <c r="T166" s="3"/>
       <c r="U166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:21" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -9286,7 +9544,7 @@
       <c r="T167" s="3"/>
       <c r="U167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:21" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -9309,7 +9567,7 @@
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:21" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -9332,7 +9590,7 @@
       <c r="T169" s="3"/>
       <c r="U169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:21" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -9355,7 +9613,7 @@
       <c r="T170" s="3"/>
       <c r="U170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:21" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -9378,7 +9636,7 @@
       <c r="T171" s="3"/>
       <c r="U171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:21" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -9401,7 +9659,7 @@
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:21" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -9424,7 +9682,7 @@
       <c r="T173" s="3"/>
       <c r="U173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:21" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -9447,7 +9705,7 @@
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:21" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -9470,7 +9728,7 @@
       <c r="T175" s="3"/>
       <c r="U175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:21" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -9493,7 +9751,7 @@
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:21" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -9516,7 +9774,7 @@
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:21" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -9539,7 +9797,7 @@
       <c r="T178" s="3"/>
       <c r="U178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:21" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -9562,7 +9820,7 @@
       <c r="T179" s="3"/>
       <c r="U179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:21" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -9585,7 +9843,7 @@
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:21" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -9608,7 +9866,7 @@
       <c r="T181" s="3"/>
       <c r="U181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:21" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -9631,7 +9889,7 @@
       <c r="T182" s="3"/>
       <c r="U182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:21" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -9654,7 +9912,7 @@
       <c r="T183" s="3"/>
       <c r="U183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:21" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -9677,7 +9935,7 @@
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:21" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -9700,7 +9958,7 @@
       <c r="T185" s="3"/>
       <c r="U185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:21" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -9723,7 +9981,7 @@
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:21" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -9746,7 +10004,7 @@
       <c r="T187" s="3"/>
       <c r="U187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:21" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -9769,7 +10027,7 @@
       <c r="T188" s="3"/>
       <c r="U188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:21" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -9792,7 +10050,7 @@
       <c r="T189" s="3"/>
       <c r="U189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:21" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -9815,7 +10073,7 @@
       <c r="T190" s="3"/>
       <c r="U190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:21" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -9838,7 +10096,7 @@
       <c r="T191" s="3"/>
       <c r="U191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:21" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -9861,7 +10119,7 @@
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:21" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -9884,7 +10142,7 @@
       <c r="T193" s="3"/>
       <c r="U193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:21" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -9907,7 +10165,7 @@
       <c r="T194" s="3"/>
       <c r="U194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:21" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -9930,7 +10188,7 @@
       <c r="T195" s="3"/>
       <c r="U195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:21" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -9953,7 +10211,7 @@
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:21" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -9976,7 +10234,7 @@
       <c r="T197" s="3"/>
       <c r="U197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:21" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -9999,7 +10257,7 @@
       <c r="T198" s="3"/>
       <c r="U198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:21" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -10022,7 +10280,7 @@
       <c r="T199" s="3"/>
       <c r="U199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:21" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -10045,7 +10303,7 @@
       <c r="T200" s="3"/>
       <c r="U200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:21" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -10068,7 +10326,7 @@
       <c r="T201" s="3"/>
       <c r="U201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:21" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -10091,7 +10349,7 @@
       <c r="T202" s="3"/>
       <c r="U202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:21" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -10114,7 +10372,7 @@
       <c r="T203" s="3"/>
       <c r="U203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:21" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -10137,7 +10395,7 @@
       <c r="T204" s="3"/>
       <c r="U204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:21" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -10160,7 +10418,7 @@
       <c r="T205" s="3"/>
       <c r="U205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:21" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -10183,8 +10441,8 @@
       <c r="T206" s="3"/>
       <c r="U206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="207" spans="1:21" ht="15.75" customHeight="1"/>
+    <row r="208" spans="1:21" ht="15.75" customHeight="1"/>
     <row r="209" ht="15.75" customHeight="1"/>
     <row r="210" ht="15.75" customHeight="1"/>
     <row r="211" ht="15.75" customHeight="1"/>
@@ -10964,28 +11222,24 @@
     <row r="985" ht="15.75" customHeight="1"/>
     <row r="986" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y1000"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.86"/>
-    <col customWidth="1" min="2" max="2" width="19.0"/>
-    <col customWidth="1" min="3" max="3" width="20.0"/>
-    <col customWidth="1" min="4" max="14" width="7.71"/>
-    <col customWidth="1" min="15" max="25" width="15.14"/>
+    <col min="1" max="1" width="16.86328125" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="14" width="7.6796875" customWidth="1"/>
+    <col min="15" max="25" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:25" ht="14.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -11022,7 +11276,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:25" ht="14.25" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -11030,8 +11284,8 @@
         <v>28</v>
       </c>
       <c r="C2" s="17" t="str">
-        <f>TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2020-04-15_09-52</v>
+        <f ca="1">TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
+        <v>2020-08-25 14-54</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>35</v>
@@ -11060,7 +11314,7 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:25" ht="14.25" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -11087,7 +11341,7 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -11114,7 +11368,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -11141,7 +11395,7 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:25" ht="14.25" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -11168,7 +11422,7 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:25" ht="14.25" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -11195,7 +11449,7 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:25" ht="14.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -11222,7 +11476,7 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:25" ht="14.25" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -11249,7 +11503,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:25" ht="14.25" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -11276,7 +11530,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:25" ht="14.25" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -11303,7 +11557,7 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:25" ht="14.25" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -11330,7 +11584,7 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:25" ht="14.25" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -11357,7 +11611,7 @@
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:25" ht="14.25" customHeight="1">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -11384,7 +11638,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:25" ht="14.25" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -11411,7 +11665,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:25" ht="14.25" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -11438,7 +11692,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:25" ht="14.25" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -11465,7 +11719,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:25" ht="14.25" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -11492,7 +11746,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:25" ht="14.25" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -11519,7 +11773,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:25" ht="14.25" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -11546,7 +11800,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:25" ht="14.25" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -11573,7 +11827,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:25" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -11600,7 +11854,7 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:25" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -11627,7 +11881,7 @@
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:25" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -11654,7 +11908,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -11681,7 +11935,7 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:25" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -11708,7 +11962,7 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:25" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -11735,7 +11989,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:25" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -11762,7 +12016,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:25" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -11789,7 +12043,7 @@
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:25" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -11816,7 +12070,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:25" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -11843,7 +12097,7 @@
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:25" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -11870,7 +12124,7 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:25" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -11897,7 +12151,7 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:25" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -11924,7 +12178,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:25" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -11951,7 +12205,7 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:25" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -11978,7 +12232,7 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:25" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -12005,7 +12259,7 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:25" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -12032,7 +12286,7 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:25" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -12059,7 +12313,7 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:25" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -12086,7 +12340,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:25" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -12113,7 +12367,7 @@
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:25" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -12140,7 +12394,7 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:25" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -12167,7 +12421,7 @@
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:25" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -12194,7 +12448,7 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:25" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -12221,7 +12475,7 @@
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:25" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -12248,7 +12502,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:25" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -12275,7 +12529,7 @@
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:25" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -12302,7 +12556,7 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:25" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -12329,7 +12583,7 @@
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:25" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -12356,7 +12610,7 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:25" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -12383,7 +12637,7 @@
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:25" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -12410,7 +12664,7 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:25" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -12437,7 +12691,7 @@
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:25" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -12464,7 +12718,7 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:25" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -12491,7 +12745,7 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:25" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -12518,7 +12772,7 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:25" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -12545,7 +12799,7 @@
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:25" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -12572,7 +12826,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:25" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -12599,7 +12853,7 @@
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:25" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -12626,7 +12880,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:25" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -12653,7 +12907,7 @@
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:25" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -12680,7 +12934,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:25" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -12707,7 +12961,7 @@
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:25" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -12734,7 +12988,7 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:25" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -12761,7 +13015,7 @@
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:25" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -12788,7 +13042,7 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:25" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -12815,7 +13069,7 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:25" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -12842,7 +13096,7 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:25" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -12869,7 +13123,7 @@
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:25" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -12896,7 +13150,7 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:25" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -12923,7 +13177,7 @@
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:25" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -12950,7 +13204,7 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:25" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -12977,7 +13231,7 @@
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:25" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -13004,7 +13258,7 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:25" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -13031,7 +13285,7 @@
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:25" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -13058,7 +13312,7 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:25" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -13085,7 +13339,7 @@
       <c r="X77" s="3"/>
       <c r="Y77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:25" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -13112,7 +13366,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:25" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -13139,7 +13393,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:25" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -13166,7 +13420,7 @@
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:25" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -13193,7 +13447,7 @@
       <c r="X81" s="3"/>
       <c r="Y81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:25" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -13220,7 +13474,7 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:25" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -13247,7 +13501,7 @@
       <c r="X83" s="3"/>
       <c r="Y83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:25" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -13274,7 +13528,7 @@
       <c r="X84" s="3"/>
       <c r="Y84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:25" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -13301,7 +13555,7 @@
       <c r="X85" s="3"/>
       <c r="Y85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:25" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -13328,7 +13582,7 @@
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:25" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -13355,7 +13609,7 @@
       <c r="X87" s="3"/>
       <c r="Y87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:25" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -13382,7 +13636,7 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:25" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -13409,7 +13663,7 @@
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:25" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -13436,7 +13690,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:25" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -13463,7 +13717,7 @@
       <c r="X91" s="3"/>
       <c r="Y91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:25" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -13490,7 +13744,7 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:25" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -13517,7 +13771,7 @@
       <c r="X93" s="3"/>
       <c r="Y93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:25" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -13544,7 +13798,7 @@
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:25" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -13571,7 +13825,7 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:25" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -13598,7 +13852,7 @@
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:25" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -13625,7 +13879,7 @@
       <c r="X97" s="3"/>
       <c r="Y97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:25" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -13652,7 +13906,7 @@
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:25" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -13679,7 +13933,7 @@
       <c r="X99" s="3"/>
       <c r="Y99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:25" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -13706,7 +13960,7 @@
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:25" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -13733,7 +13987,7 @@
       <c r="X101" s="3"/>
       <c r="Y101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:25" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -13760,7 +14014,7 @@
       <c r="X102" s="3"/>
       <c r="Y102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:25" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -13787,7 +14041,7 @@
       <c r="X103" s="3"/>
       <c r="Y103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:25" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -13814,7 +14068,7 @@
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:25" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -13841,7 +14095,7 @@
       <c r="X105" s="3"/>
       <c r="Y105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:25" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -13868,7 +14122,7 @@
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:25" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -13895,7 +14149,7 @@
       <c r="X107" s="3"/>
       <c r="Y107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:25" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -13922,7 +14176,7 @@
       <c r="X108" s="3"/>
       <c r="Y108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:25" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -13949,7 +14203,7 @@
       <c r="X109" s="3"/>
       <c r="Y109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:25" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -13976,7 +14230,7 @@
       <c r="X110" s="3"/>
       <c r="Y110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:25" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -14003,7 +14257,7 @@
       <c r="X111" s="3"/>
       <c r="Y111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:25" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -14030,7 +14284,7 @@
       <c r="X112" s="3"/>
       <c r="Y112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:25" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -14057,7 +14311,7 @@
       <c r="X113" s="3"/>
       <c r="Y113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:25" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -14084,7 +14338,7 @@
       <c r="X114" s="3"/>
       <c r="Y114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:25" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -14111,7 +14365,7 @@
       <c r="X115" s="3"/>
       <c r="Y115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:25" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -14138,7 +14392,7 @@
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:25" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -14165,7 +14419,7 @@
       <c r="X117" s="3"/>
       <c r="Y117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:25" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -14192,7 +14446,7 @@
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:25" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -14219,7 +14473,7 @@
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:25" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -14246,7 +14500,7 @@
       <c r="X120" s="3"/>
       <c r="Y120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:25" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -14273,7 +14527,7 @@
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:25" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -14300,7 +14554,7 @@
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:25" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -14327,7 +14581,7 @@
       <c r="X123" s="3"/>
       <c r="Y123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:25" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -14354,7 +14608,7 @@
       <c r="X124" s="3"/>
       <c r="Y124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:25" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -14381,7 +14635,7 @@
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:25" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -14408,7 +14662,7 @@
       <c r="X126" s="3"/>
       <c r="Y126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:25" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -14435,7 +14689,7 @@
       <c r="X127" s="3"/>
       <c r="Y127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:25" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -14462,7 +14716,7 @@
       <c r="X128" s="3"/>
       <c r="Y128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:25" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -14489,7 +14743,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:25" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -14516,7 +14770,7 @@
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:25" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -14543,7 +14797,7 @@
       <c r="X131" s="3"/>
       <c r="Y131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:25" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -14570,7 +14824,7 @@
       <c r="X132" s="3"/>
       <c r="Y132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:25" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -14597,7 +14851,7 @@
       <c r="X133" s="3"/>
       <c r="Y133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:25" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -14624,7 +14878,7 @@
       <c r="X134" s="3"/>
       <c r="Y134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:25" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -14651,7 +14905,7 @@
       <c r="X135" s="3"/>
       <c r="Y135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:25" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -14678,7 +14932,7 @@
       <c r="X136" s="3"/>
       <c r="Y136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:25" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -14705,7 +14959,7 @@
       <c r="X137" s="3"/>
       <c r="Y137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:25" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -14732,7 +14986,7 @@
       <c r="X138" s="3"/>
       <c r="Y138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:25" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -14759,7 +15013,7 @@
       <c r="X139" s="3"/>
       <c r="Y139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:25" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -14786,7 +15040,7 @@
       <c r="X140" s="3"/>
       <c r="Y140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:25" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -14813,7 +15067,7 @@
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:25" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -14840,7 +15094,7 @@
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:25" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -14867,7 +15121,7 @@
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:25" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -14894,7 +15148,7 @@
       <c r="X144" s="3"/>
       <c r="Y144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:25" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -14921,7 +15175,7 @@
       <c r="X145" s="3"/>
       <c r="Y145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:25" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -14948,7 +15202,7 @@
       <c r="X146" s="3"/>
       <c r="Y146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:25" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -14975,7 +15229,7 @@
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:25" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -15002,7 +15256,7 @@
       <c r="X148" s="3"/>
       <c r="Y148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:25" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -15029,7 +15283,7 @@
       <c r="X149" s="3"/>
       <c r="Y149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:25" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -15056,7 +15310,7 @@
       <c r="X150" s="3"/>
       <c r="Y150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:25" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -15083,7 +15337,7 @@
       <c r="X151" s="3"/>
       <c r="Y151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:25" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -15110,7 +15364,7 @@
       <c r="X152" s="3"/>
       <c r="Y152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:25" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -15137,7 +15391,7 @@
       <c r="X153" s="3"/>
       <c r="Y153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:25" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -15164,7 +15418,7 @@
       <c r="X154" s="3"/>
       <c r="Y154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:25" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -15191,7 +15445,7 @@
       <c r="X155" s="3"/>
       <c r="Y155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:25" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -15218,7 +15472,7 @@
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:25" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -15245,7 +15499,7 @@
       <c r="X157" s="3"/>
       <c r="Y157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:25" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -15272,7 +15526,7 @@
       <c r="X158" s="3"/>
       <c r="Y158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:25" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -15299,7 +15553,7 @@
       <c r="X159" s="3"/>
       <c r="Y159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:25" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -15326,7 +15580,7 @@
       <c r="X160" s="3"/>
       <c r="Y160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:25" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -15353,7 +15607,7 @@
       <c r="X161" s="3"/>
       <c r="Y161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:25" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -15380,7 +15634,7 @@
       <c r="X162" s="3"/>
       <c r="Y162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:25" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -15407,7 +15661,7 @@
       <c r="X163" s="3"/>
       <c r="Y163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:25" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -15434,7 +15688,7 @@
       <c r="X164" s="3"/>
       <c r="Y164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:25" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -15461,7 +15715,7 @@
       <c r="X165" s="3"/>
       <c r="Y165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:25" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -15488,7 +15742,7 @@
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:25" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -15515,7 +15769,7 @@
       <c r="X167" s="3"/>
       <c r="Y167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:25" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -15542,7 +15796,7 @@
       <c r="X168" s="3"/>
       <c r="Y168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:25" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -15569,7 +15823,7 @@
       <c r="X169" s="3"/>
       <c r="Y169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:25" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -15596,7 +15850,7 @@
       <c r="X170" s="3"/>
       <c r="Y170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:25" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -15623,7 +15877,7 @@
       <c r="X171" s="3"/>
       <c r="Y171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:25" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -15650,7 +15904,7 @@
       <c r="X172" s="3"/>
       <c r="Y172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:25" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -15677,7 +15931,7 @@
       <c r="X173" s="3"/>
       <c r="Y173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:25" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -15704,7 +15958,7 @@
       <c r="X174" s="3"/>
       <c r="Y174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:25" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -15731,7 +15985,7 @@
       <c r="X175" s="3"/>
       <c r="Y175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:25" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -15758,7 +16012,7 @@
       <c r="X176" s="3"/>
       <c r="Y176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:25" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -15785,7 +16039,7 @@
       <c r="X177" s="3"/>
       <c r="Y177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:25" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -15812,7 +16066,7 @@
       <c r="X178" s="3"/>
       <c r="Y178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:25" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -15839,7 +16093,7 @@
       <c r="X179" s="3"/>
       <c r="Y179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:25" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -15866,7 +16120,7 @@
       <c r="X180" s="3"/>
       <c r="Y180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:25" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -15893,7 +16147,7 @@
       <c r="X181" s="3"/>
       <c r="Y181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:25" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -15920,7 +16174,7 @@
       <c r="X182" s="3"/>
       <c r="Y182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:25" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -15947,7 +16201,7 @@
       <c r="X183" s="3"/>
       <c r="Y183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:25" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -15974,7 +16228,7 @@
       <c r="X184" s="3"/>
       <c r="Y184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:25" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -16001,7 +16255,7 @@
       <c r="X185" s="3"/>
       <c r="Y185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:25" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -16028,7 +16282,7 @@
       <c r="X186" s="3"/>
       <c r="Y186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:25" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -16055,7 +16309,7 @@
       <c r="X187" s="3"/>
       <c r="Y187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:25" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -16082,7 +16336,7 @@
       <c r="X188" s="3"/>
       <c r="Y188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:25" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -16109,7 +16363,7 @@
       <c r="X189" s="3"/>
       <c r="Y189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:25" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -16136,7 +16390,7 @@
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:25" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -16163,7 +16417,7 @@
       <c r="X191" s="3"/>
       <c r="Y191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:25" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -16190,7 +16444,7 @@
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:25" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -16217,7 +16471,7 @@
       <c r="X193" s="3"/>
       <c r="Y193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:25" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -16244,7 +16498,7 @@
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:25" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -16271,7 +16525,7 @@
       <c r="X195" s="3"/>
       <c r="Y195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:25" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -16298,7 +16552,7 @@
       <c r="X196" s="3"/>
       <c r="Y196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:25" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -16325,7 +16579,7 @@
       <c r="X197" s="3"/>
       <c r="Y197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:25" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -16352,7 +16606,7 @@
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:25" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -16379,7 +16633,7 @@
       <c r="X199" s="3"/>
       <c r="Y199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:25" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -16406,7 +16660,7 @@
       <c r="X200" s="3"/>
       <c r="Y200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:25" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -16433,7 +16687,7 @@
       <c r="X201" s="3"/>
       <c r="Y201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:25" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -16460,7 +16714,7 @@
       <c r="X202" s="3"/>
       <c r="Y202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:25" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -16487,7 +16741,7 @@
       <c r="X203" s="3"/>
       <c r="Y203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:25" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -16514,7 +16768,7 @@
       <c r="X204" s="3"/>
       <c r="Y204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:25" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -16541,7 +16795,7 @@
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:25" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -16568,7 +16822,7 @@
       <c r="X206" s="3"/>
       <c r="Y206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:25" ht="15.75" customHeight="1">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -16595,7 +16849,7 @@
       <c r="X207" s="3"/>
       <c r="Y207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:25" ht="15.75" customHeight="1">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -16622,7 +16876,7 @@
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:25" ht="15.75" customHeight="1">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -16649,7 +16903,7 @@
       <c r="X209" s="3"/>
       <c r="Y209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:25" ht="15.75" customHeight="1">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -16676,7 +16930,7 @@
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:25" ht="15.75" customHeight="1">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -16703,7 +16957,7 @@
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:25" ht="15.75" customHeight="1">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -16730,7 +16984,7 @@
       <c r="X212" s="3"/>
       <c r="Y212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:25" ht="15.75" customHeight="1">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -16757,7 +17011,7 @@
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:25" ht="15.75" customHeight="1">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -16784,7 +17038,7 @@
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:25" ht="15.75" customHeight="1">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -16811,7 +17065,7 @@
       <c r="X215" s="3"/>
       <c r="Y215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:25" ht="15.75" customHeight="1">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -16838,7 +17092,7 @@
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:25" ht="15.75" customHeight="1">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -16865,7 +17119,7 @@
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:25" ht="15.75" customHeight="1">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -16892,7 +17146,7 @@
       <c r="X218" s="3"/>
       <c r="Y218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:25" ht="15.75" customHeight="1">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -16919,7 +17173,7 @@
       <c r="X219" s="3"/>
       <c r="Y219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:25" ht="15.75" customHeight="1">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -16946,10 +17200,10 @@
       <c r="X220" s="3"/>
       <c r="Y220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -17727,9 +17981,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/forms/contact/person-edit.xlsx
+++ b/forms/contact/person-edit.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="116">
   <si>
     <t>type</t>
   </si>
@@ -628,7 +628,7 @@
     <col customWidth="1" min="3" max="3" width="27.86"/>
     <col customWidth="1" min="4" max="4" width="28.71"/>
     <col customWidth="1" min="5" max="5" width="15.57"/>
-    <col customWidth="1" min="6" max="6" width="14.57"/>
+    <col customWidth="1" min="6" max="6" width="19.86"/>
     <col customWidth="1" min="7" max="7" width="19.57"/>
     <col customWidth="1" min="8" max="8" width="10.71"/>
     <col customWidth="1" min="9" max="9" width="24.14"/>
@@ -1368,7 +1368,9 @@
       <c r="D19" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -11032,7 +11034,7 @@
       </c>
       <c r="C2" s="34" t="str">
         <f>TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2020-10-06_09-33</v>
+        <v>2020-11-03_06-50</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>114</v>

--- a/forms/contact/person-edit.xlsx
+++ b/forms/contact/person-edit.xlsx
@@ -3,12 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId5"/>
+    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="wI2bBtiHyP+9cXZpLfzTghQwCWApUslFHCZ/qiWGEUo="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -141,8 +146,7 @@
 •        Epuka mikusanyiko. 
 •        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
 •        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
-•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
-</t>
+•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">end group </t>
@@ -383,23 +387,35 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF1D1C1D"/>
-      <name val="Slack-Lato"/>
+      <name val="Lato"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -441,16 +457,10 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border/>
     <border>
       <left/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom/>
     </border>
@@ -469,7 +479,6 @@
       </bottom>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FFB2B2B2"/>
       </right>
@@ -484,108 +493,81 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -616,6 +598,200 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="0000FF"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -684,7 +860,7 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -704,31 +880,31 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="5">
+      <c r="F2" s="1">
         <v>0.0</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="10"/>
+      <c r="O2" s="4"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -744,16 +920,16 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="1"/>
@@ -761,12 +937,12 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="9"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="10"/>
+      <c r="O3" s="4"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -782,54 +958,54 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="1"/>
@@ -837,12 +1013,12 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="10"/>
+      <c r="O5" s="4"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -858,16 +1034,16 @@
       <c r="AB5" s="1"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="1"/>
@@ -875,12 +1051,12 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="10"/>
+      <c r="O6" s="4"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -896,25 +1072,25 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="9"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="4"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
@@ -930,25 +1106,25 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="9"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="10"/>
+      <c r="O8" s="4"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
@@ -964,33 +1140,33 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -1002,33 +1178,33 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
@@ -1040,29 +1216,29 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
@@ -1074,31 +1250,31 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="10"/>
+      <c r="O12" s="4"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1114,31 +1290,31 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="16"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="10"/>
+      <c r="O13" s="4"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1154,32 +1330,32 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="16"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="5" t="s">
+      <c r="O14" s="4"/>
+      <c r="P14" s="1" t="s">
         <v>39</v>
       </c>
       <c r="Q14" s="1"/>
@@ -1196,31 +1372,31 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="4"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -1236,31 +1412,31 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="4"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-      <c r="O16" s="10"/>
+      <c r="O16" s="4"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -1276,31 +1452,31 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="10"/>
+      <c r="O17" s="4"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -1316,31 +1492,31 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="9"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="4"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="9"/>
+      <c r="O18" s="4"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1356,35 +1532,35 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="9"/>
+      <c r="K19" s="4"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="10"/>
+      <c r="O19" s="4"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -1400,44 +1576,44 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="19" t="b">
+      <c r="I20" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="L20" s="21"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="9"/>
+      <c r="O20" s="4"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="5" t="s">
+      <c r="R20" s="1" t="s">
         <v>46</v>
       </c>
       <c r="S20" s="1"/>
@@ -1452,39 +1628,39 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="19" t="b">
+      <c r="I21" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="20" t="s">
+      <c r="K21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="L21" s="21"/>
+      <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="9"/>
+      <c r="O21" s="4"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -1500,33 +1676,33 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="10"/>
+      <c r="O22" s="4"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -1542,3060 +1718,3060 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="23"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23" t="s">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="24" t="s">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="23"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="15"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="15"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="24" t="s">
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="7" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="9"/>
+      <c r="O27" s="4"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="7" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="O28" s="10"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="O28" s="4"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
-      <c r="AA29" s="9"/>
-      <c r="AB29" s="9"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="4"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="5" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-      <c r="AB31" s="9"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="4"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="7" t="s">
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="9"/>
-      <c r="AB32" s="9"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="4"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="7" t="s">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="17" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="7" t="s">
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="4"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="O35" s="10"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="O35" s="4"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="O36" s="10"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="O36" s="4"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="9"/>
+      <c r="D37" s="4"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="9"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="4"/>
       <c r="L37" s="1"/>
-      <c r="O37" s="10"/>
+      <c r="O37" s="4"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="9"/>
+      <c r="D38" s="4"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="9"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="4"/>
       <c r="L38" s="1"/>
-      <c r="O38" s="10"/>
+      <c r="O38" s="4"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="9"/>
+      <c r="D39" s="4"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="9"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="4"/>
       <c r="L39" s="1"/>
-      <c r="O39" s="10"/>
+      <c r="O39" s="4"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="9"/>
+      <c r="D40" s="4"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="9"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="1"/>
-      <c r="O40" s="10"/>
+      <c r="O40" s="4"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="9"/>
+      <c r="D41" s="4"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="9"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="4"/>
       <c r="L41" s="1"/>
-      <c r="O41" s="10"/>
+      <c r="O41" s="4"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="9"/>
+      <c r="D42" s="4"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="9"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="4"/>
       <c r="L42" s="1"/>
-      <c r="O42" s="10"/>
+      <c r="O42" s="4"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="9"/>
+      <c r="D43" s="4"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="9"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="4"/>
       <c r="L43" s="1"/>
-      <c r="O43" s="10"/>
+      <c r="O43" s="4"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="9"/>
+      <c r="D44" s="4"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="9"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="4"/>
       <c r="L44" s="1"/>
-      <c r="O44" s="10"/>
+      <c r="O44" s="4"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="9"/>
+      <c r="D45" s="4"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="9"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="4"/>
       <c r="L45" s="1"/>
-      <c r="O45" s="10"/>
+      <c r="O45" s="4"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="9"/>
+      <c r="D46" s="4"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="9"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="4"/>
       <c r="L46" s="1"/>
-      <c r="O46" s="10"/>
+      <c r="O46" s="4"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="9"/>
+      <c r="D47" s="4"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="9"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="4"/>
       <c r="L47" s="1"/>
-      <c r="O47" s="10"/>
+      <c r="O47" s="4"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="9"/>
+      <c r="D48" s="4"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="9"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="4"/>
       <c r="L48" s="1"/>
-      <c r="O48" s="10"/>
+      <c r="O48" s="4"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="9"/>
+      <c r="D49" s="4"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="9"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="4"/>
       <c r="L49" s="1"/>
-      <c r="O49" s="10"/>
+      <c r="O49" s="4"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="9"/>
+      <c r="D50" s="4"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="9"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="4"/>
       <c r="L50" s="1"/>
-      <c r="O50" s="10"/>
+      <c r="O50" s="4"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="9"/>
+      <c r="D51" s="4"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="9"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="4"/>
       <c r="L51" s="1"/>
-      <c r="O51" s="10"/>
+      <c r="O51" s="4"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="9"/>
+      <c r="D52" s="4"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="9"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="4"/>
       <c r="L52" s="1"/>
-      <c r="O52" s="10"/>
+      <c r="O52" s="4"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="9"/>
+      <c r="D53" s="4"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="9"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="4"/>
       <c r="L53" s="1"/>
-      <c r="O53" s="10"/>
+      <c r="O53" s="4"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="9"/>
+      <c r="D54" s="4"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="9"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="4"/>
       <c r="L54" s="1"/>
-      <c r="O54" s="10"/>
+      <c r="O54" s="4"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="9"/>
+      <c r="D55" s="4"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="9"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="4"/>
       <c r="L55" s="1"/>
-      <c r="O55" s="10"/>
+      <c r="O55" s="4"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="9"/>
+      <c r="D56" s="4"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="9"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="4"/>
       <c r="L56" s="1"/>
-      <c r="O56" s="10"/>
+      <c r="O56" s="4"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="9"/>
+      <c r="D57" s="4"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="9"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="4"/>
       <c r="L57" s="1"/>
-      <c r="O57" s="10"/>
+      <c r="O57" s="4"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="9"/>
+      <c r="D58" s="4"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="9"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="4"/>
       <c r="L58" s="1"/>
-      <c r="O58" s="10"/>
+      <c r="O58" s="4"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="9"/>
+      <c r="D59" s="4"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="9"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="4"/>
       <c r="L59" s="1"/>
-      <c r="O59" s="10"/>
+      <c r="O59" s="4"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="9"/>
+      <c r="D60" s="4"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="9"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="4"/>
       <c r="L60" s="1"/>
-      <c r="O60" s="10"/>
+      <c r="O60" s="4"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="4"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="9"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="4"/>
       <c r="L61" s="1"/>
-      <c r="O61" s="10"/>
+      <c r="O61" s="4"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="9"/>
+      <c r="D62" s="4"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="9"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="1"/>
-      <c r="O62" s="10"/>
+      <c r="O62" s="4"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="9"/>
+      <c r="D63" s="4"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="9"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="4"/>
       <c r="L63" s="1"/>
-      <c r="O63" s="10"/>
+      <c r="O63" s="4"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="9"/>
+      <c r="D64" s="4"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="9"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="4"/>
       <c r="L64" s="1"/>
-      <c r="O64" s="10"/>
+      <c r="O64" s="4"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="9"/>
+      <c r="D65" s="4"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="9"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="4"/>
       <c r="L65" s="1"/>
-      <c r="O65" s="10"/>
+      <c r="O65" s="4"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="4"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="9"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="4"/>
       <c r="L66" s="1"/>
-      <c r="O66" s="10"/>
+      <c r="O66" s="4"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="4"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="9"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="4"/>
       <c r="L67" s="1"/>
-      <c r="O67" s="10"/>
+      <c r="O67" s="4"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="4"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="9"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="4"/>
       <c r="L68" s="1"/>
-      <c r="O68" s="10"/>
+      <c r="O68" s="4"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="9"/>
+      <c r="D69" s="4"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="9"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="4"/>
       <c r="L69" s="1"/>
-      <c r="O69" s="10"/>
+      <c r="O69" s="4"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="9"/>
+      <c r="D70" s="4"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="9"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="4"/>
       <c r="L70" s="1"/>
-      <c r="O70" s="10"/>
+      <c r="O70" s="4"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="9"/>
+      <c r="D71" s="4"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="9"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="4"/>
       <c r="L71" s="1"/>
-      <c r="O71" s="10"/>
+      <c r="O71" s="4"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="9"/>
+      <c r="D72" s="4"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="9"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="4"/>
       <c r="L72" s="1"/>
-      <c r="O72" s="10"/>
+      <c r="O72" s="4"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="9"/>
+      <c r="D73" s="4"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="9"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="4"/>
       <c r="L73" s="1"/>
-      <c r="O73" s="10"/>
+      <c r="O73" s="4"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="9"/>
+      <c r="D74" s="4"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="9"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="4"/>
       <c r="L74" s="1"/>
-      <c r="O74" s="10"/>
+      <c r="O74" s="4"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="9"/>
+      <c r="D75" s="4"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="9"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="4"/>
       <c r="L75" s="1"/>
-      <c r="O75" s="10"/>
+      <c r="O75" s="4"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="9"/>
+      <c r="D76" s="4"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="9"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="4"/>
       <c r="L76" s="1"/>
-      <c r="O76" s="10"/>
+      <c r="O76" s="4"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="9"/>
+      <c r="D77" s="4"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="9"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="4"/>
       <c r="L77" s="1"/>
-      <c r="O77" s="10"/>
+      <c r="O77" s="4"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="9"/>
+      <c r="D78" s="4"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="9"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="4"/>
       <c r="L78" s="1"/>
-      <c r="O78" s="10"/>
+      <c r="O78" s="4"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="9"/>
+      <c r="D79" s="4"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="9"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="4"/>
       <c r="L79" s="1"/>
-      <c r="O79" s="10"/>
+      <c r="O79" s="4"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="9"/>
+      <c r="D80" s="4"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="9"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="4"/>
       <c r="L80" s="1"/>
-      <c r="O80" s="10"/>
+      <c r="O80" s="4"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="9"/>
+      <c r="D81" s="4"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="9"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="4"/>
       <c r="L81" s="1"/>
-      <c r="O81" s="10"/>
+      <c r="O81" s="4"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="9"/>
+      <c r="D82" s="4"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="9"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="4"/>
       <c r="L82" s="1"/>
-      <c r="O82" s="10"/>
+      <c r="O82" s="4"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="9"/>
+      <c r="D83" s="4"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="9"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="4"/>
       <c r="L83" s="1"/>
-      <c r="O83" s="10"/>
+      <c r="O83" s="4"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="9"/>
+      <c r="D84" s="4"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="9"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="4"/>
       <c r="L84" s="1"/>
-      <c r="O84" s="10"/>
+      <c r="O84" s="4"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="9"/>
+      <c r="D85" s="4"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="9"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="4"/>
       <c r="L85" s="1"/>
-      <c r="O85" s="10"/>
+      <c r="O85" s="4"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="9"/>
+      <c r="D86" s="4"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="9"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="4"/>
       <c r="L86" s="1"/>
-      <c r="O86" s="10"/>
+      <c r="O86" s="4"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="9"/>
+      <c r="D87" s="4"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="9"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="4"/>
       <c r="L87" s="1"/>
-      <c r="O87" s="10"/>
+      <c r="O87" s="4"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="2"/>
-      <c r="D88" s="9"/>
+      <c r="D88" s="4"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="9"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="4"/>
       <c r="L88" s="1"/>
-      <c r="O88" s="10"/>
+      <c r="O88" s="4"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="2"/>
-      <c r="D89" s="9"/>
+      <c r="D89" s="4"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="9"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="4"/>
       <c r="L89" s="1"/>
-      <c r="O89" s="10"/>
+      <c r="O89" s="4"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="9"/>
+      <c r="D90" s="4"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="9"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="4"/>
       <c r="L90" s="1"/>
-      <c r="O90" s="10"/>
+      <c r="O90" s="4"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="9"/>
+      <c r="D91" s="4"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="9"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="4"/>
       <c r="L91" s="1"/>
-      <c r="O91" s="10"/>
+      <c r="O91" s="4"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="9"/>
+      <c r="D92" s="4"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="9"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="4"/>
       <c r="L92" s="1"/>
-      <c r="O92" s="10"/>
+      <c r="O92" s="4"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="9"/>
+      <c r="D93" s="4"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="9"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="4"/>
       <c r="L93" s="1"/>
-      <c r="O93" s="10"/>
+      <c r="O93" s="4"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="2"/>
-      <c r="D94" s="9"/>
+      <c r="D94" s="4"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="9"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="4"/>
       <c r="L94" s="1"/>
-      <c r="O94" s="10"/>
+      <c r="O94" s="4"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="9"/>
+      <c r="D95" s="4"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="9"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="4"/>
       <c r="L95" s="1"/>
-      <c r="O95" s="10"/>
+      <c r="O95" s="4"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="2"/>
-      <c r="D96" s="9"/>
+      <c r="D96" s="4"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="9"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="4"/>
       <c r="L96" s="1"/>
-      <c r="O96" s="10"/>
+      <c r="O96" s="4"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="9"/>
+      <c r="D97" s="4"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="9"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="4"/>
       <c r="L97" s="1"/>
-      <c r="O97" s="10"/>
+      <c r="O97" s="4"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="9"/>
+      <c r="D98" s="4"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="9"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="4"/>
       <c r="L98" s="1"/>
-      <c r="O98" s="10"/>
+      <c r="O98" s="4"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="9"/>
+      <c r="D99" s="4"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="9"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="4"/>
       <c r="L99" s="1"/>
-      <c r="O99" s="10"/>
+      <c r="O99" s="4"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="2"/>
-      <c r="D100" s="9"/>
+      <c r="D100" s="4"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="9"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="4"/>
       <c r="L100" s="1"/>
-      <c r="O100" s="10"/>
+      <c r="O100" s="4"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="9"/>
+      <c r="D101" s="4"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="9"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="4"/>
       <c r="L101" s="1"/>
-      <c r="O101" s="10"/>
+      <c r="O101" s="4"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="9"/>
+      <c r="D102" s="4"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="9"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="4"/>
       <c r="L102" s="1"/>
-      <c r="O102" s="10"/>
+      <c r="O102" s="4"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="9"/>
+      <c r="D103" s="4"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="9"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="4"/>
       <c r="L103" s="1"/>
-      <c r="O103" s="10"/>
+      <c r="O103" s="4"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="9"/>
+      <c r="D104" s="4"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="9"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="4"/>
       <c r="L104" s="1"/>
-      <c r="O104" s="10"/>
+      <c r="O104" s="4"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="9"/>
+      <c r="D105" s="4"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="9"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="4"/>
       <c r="L105" s="1"/>
-      <c r="O105" s="10"/>
+      <c r="O105" s="4"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="9"/>
+      <c r="D106" s="4"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="9"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="4"/>
       <c r="L106" s="1"/>
-      <c r="O106" s="10"/>
+      <c r="O106" s="4"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="9"/>
+      <c r="D107" s="4"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
-      <c r="J107" s="8"/>
-      <c r="K107" s="9"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="4"/>
       <c r="L107" s="1"/>
-      <c r="O107" s="10"/>
+      <c r="O107" s="4"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="9"/>
+      <c r="D108" s="4"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
-      <c r="J108" s="8"/>
-      <c r="K108" s="9"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="4"/>
       <c r="L108" s="1"/>
-      <c r="O108" s="10"/>
+      <c r="O108" s="4"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="9"/>
+      <c r="D109" s="4"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="9"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="4"/>
       <c r="L109" s="1"/>
-      <c r="O109" s="10"/>
+      <c r="O109" s="4"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="9"/>
+      <c r="D110" s="4"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="9"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="4"/>
       <c r="L110" s="1"/>
-      <c r="O110" s="10"/>
+      <c r="O110" s="4"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="9"/>
+      <c r="D111" s="4"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="9"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="4"/>
       <c r="L111" s="1"/>
-      <c r="O111" s="10"/>
+      <c r="O111" s="4"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="9"/>
+      <c r="D112" s="4"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
-      <c r="J112" s="8"/>
-      <c r="K112" s="9"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="4"/>
       <c r="L112" s="1"/>
-      <c r="O112" s="10"/>
+      <c r="O112" s="4"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="9"/>
+      <c r="D113" s="4"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="9"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="4"/>
       <c r="L113" s="1"/>
-      <c r="O113" s="10"/>
+      <c r="O113" s="4"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="9"/>
+      <c r="D114" s="4"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
-      <c r="J114" s="8"/>
-      <c r="K114" s="9"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="4"/>
       <c r="L114" s="1"/>
-      <c r="O114" s="10"/>
+      <c r="O114" s="4"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="9"/>
+      <c r="D115" s="4"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="9"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="4"/>
       <c r="L115" s="1"/>
-      <c r="O115" s="10"/>
+      <c r="O115" s="4"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="9"/>
+      <c r="D116" s="4"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
-      <c r="J116" s="8"/>
-      <c r="K116" s="9"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="4"/>
       <c r="L116" s="1"/>
-      <c r="O116" s="10"/>
+      <c r="O116" s="4"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="9"/>
+      <c r="D117" s="4"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
-      <c r="J117" s="8"/>
-      <c r="K117" s="9"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="4"/>
       <c r="L117" s="1"/>
-      <c r="O117" s="10"/>
+      <c r="O117" s="4"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="9"/>
+      <c r="D118" s="4"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
-      <c r="J118" s="8"/>
-      <c r="K118" s="9"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="4"/>
       <c r="L118" s="1"/>
-      <c r="O118" s="10"/>
+      <c r="O118" s="4"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="9"/>
+      <c r="D119" s="4"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
-      <c r="J119" s="8"/>
-      <c r="K119" s="9"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="4"/>
       <c r="L119" s="1"/>
-      <c r="O119" s="10"/>
+      <c r="O119" s="4"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="9"/>
+      <c r="D120" s="4"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
-      <c r="J120" s="8"/>
-      <c r="K120" s="9"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="4"/>
       <c r="L120" s="1"/>
-      <c r="O120" s="10"/>
+      <c r="O120" s="4"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="9"/>
+      <c r="D121" s="4"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="9"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="4"/>
       <c r="L121" s="1"/>
-      <c r="O121" s="10"/>
+      <c r="O121" s="4"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="9"/>
+      <c r="D122" s="4"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="9"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="4"/>
       <c r="L122" s="1"/>
-      <c r="O122" s="10"/>
+      <c r="O122" s="4"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="9"/>
+      <c r="D123" s="4"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="9"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="4"/>
       <c r="L123" s="1"/>
-      <c r="O123" s="10"/>
+      <c r="O123" s="4"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="9"/>
+      <c r="D124" s="4"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="9"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="4"/>
       <c r="L124" s="1"/>
-      <c r="O124" s="10"/>
+      <c r="O124" s="4"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="9"/>
+      <c r="D125" s="4"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
-      <c r="J125" s="8"/>
-      <c r="K125" s="9"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="4"/>
       <c r="L125" s="1"/>
-      <c r="O125" s="10"/>
+      <c r="O125" s="4"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="9"/>
+      <c r="D126" s="4"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
-      <c r="J126" s="8"/>
-      <c r="K126" s="9"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="4"/>
       <c r="L126" s="1"/>
-      <c r="O126" s="10"/>
+      <c r="O126" s="4"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="9"/>
+      <c r="D127" s="4"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="9"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="4"/>
       <c r="L127" s="1"/>
-      <c r="O127" s="10"/>
+      <c r="O127" s="4"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="9"/>
+      <c r="D128" s="4"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="9"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="4"/>
       <c r="L128" s="1"/>
-      <c r="O128" s="10"/>
+      <c r="O128" s="4"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="9"/>
+      <c r="D129" s="4"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
-      <c r="J129" s="8"/>
-      <c r="K129" s="9"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="4"/>
       <c r="L129" s="1"/>
-      <c r="O129" s="10"/>
+      <c r="O129" s="4"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="9"/>
+      <c r="D130" s="4"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="9"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="4"/>
       <c r="L130" s="1"/>
-      <c r="O130" s="10"/>
+      <c r="O130" s="4"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="9"/>
+      <c r="D131" s="4"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="9"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="4"/>
       <c r="L131" s="1"/>
-      <c r="O131" s="10"/>
+      <c r="O131" s="4"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="9"/>
+      <c r="D132" s="4"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
-      <c r="J132" s="8"/>
-      <c r="K132" s="9"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="4"/>
       <c r="L132" s="1"/>
-      <c r="O132" s="10"/>
+      <c r="O132" s="4"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="9"/>
+      <c r="D133" s="4"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
-      <c r="J133" s="8"/>
-      <c r="K133" s="9"/>
+      <c r="J133" s="5"/>
+      <c r="K133" s="4"/>
       <c r="L133" s="1"/>
-      <c r="O133" s="10"/>
+      <c r="O133" s="4"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="9"/>
+      <c r="D134" s="4"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
-      <c r="J134" s="8"/>
-      <c r="K134" s="9"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="4"/>
       <c r="L134" s="1"/>
-      <c r="O134" s="10"/>
+      <c r="O134" s="4"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="9"/>
+      <c r="D135" s="4"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="9"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="4"/>
       <c r="L135" s="1"/>
-      <c r="O135" s="10"/>
+      <c r="O135" s="4"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="9"/>
+      <c r="D136" s="4"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="9"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="4"/>
       <c r="L136" s="1"/>
-      <c r="O136" s="10"/>
+      <c r="O136" s="4"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="9"/>
+      <c r="D137" s="4"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="9"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="4"/>
       <c r="L137" s="1"/>
-      <c r="O137" s="10"/>
+      <c r="O137" s="4"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="9"/>
+      <c r="D138" s="4"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="9"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="4"/>
       <c r="L138" s="1"/>
-      <c r="O138" s="10"/>
+      <c r="O138" s="4"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="9"/>
+      <c r="D139" s="4"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="9"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="4"/>
       <c r="L139" s="1"/>
-      <c r="O139" s="10"/>
+      <c r="O139" s="4"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="9"/>
+      <c r="D140" s="4"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
-      <c r="J140" s="8"/>
-      <c r="K140" s="9"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="4"/>
       <c r="L140" s="1"/>
-      <c r="O140" s="10"/>
+      <c r="O140" s="4"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="9"/>
+      <c r="D141" s="4"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
-      <c r="J141" s="8"/>
-      <c r="K141" s="9"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="4"/>
       <c r="L141" s="1"/>
-      <c r="O141" s="10"/>
+      <c r="O141" s="4"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="9"/>
+      <c r="D142" s="4"/>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
-      <c r="J142" s="8"/>
-      <c r="K142" s="9"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="4"/>
       <c r="L142" s="1"/>
-      <c r="O142" s="10"/>
+      <c r="O142" s="4"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="9"/>
+      <c r="D143" s="4"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="9"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="4"/>
       <c r="L143" s="1"/>
-      <c r="O143" s="10"/>
+      <c r="O143" s="4"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="9"/>
+      <c r="D144" s="4"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
-      <c r="J144" s="8"/>
-      <c r="K144" s="9"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="4"/>
       <c r="L144" s="1"/>
-      <c r="O144" s="10"/>
+      <c r="O144" s="4"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="9"/>
+      <c r="D145" s="4"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
-      <c r="J145" s="8"/>
-      <c r="K145" s="9"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="4"/>
       <c r="L145" s="1"/>
-      <c r="O145" s="10"/>
+      <c r="O145" s="4"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="9"/>
+      <c r="D146" s="4"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
-      <c r="J146" s="8"/>
-      <c r="K146" s="9"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="4"/>
       <c r="L146" s="1"/>
-      <c r="O146" s="10"/>
+      <c r="O146" s="4"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="9"/>
+      <c r="D147" s="4"/>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
-      <c r="J147" s="8"/>
-      <c r="K147" s="9"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="4"/>
       <c r="L147" s="1"/>
-      <c r="O147" s="10"/>
+      <c r="O147" s="4"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="9"/>
+      <c r="D148" s="4"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
-      <c r="J148" s="8"/>
-      <c r="K148" s="9"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="4"/>
       <c r="L148" s="1"/>
-      <c r="O148" s="10"/>
+      <c r="O148" s="4"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="9"/>
+      <c r="D149" s="4"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
-      <c r="J149" s="8"/>
-      <c r="K149" s="9"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="4"/>
       <c r="L149" s="1"/>
-      <c r="O149" s="10"/>
+      <c r="O149" s="4"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="9"/>
+      <c r="D150" s="4"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
-      <c r="J150" s="8"/>
-      <c r="K150" s="9"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="4"/>
       <c r="L150" s="1"/>
-      <c r="O150" s="10"/>
+      <c r="O150" s="4"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="9"/>
+      <c r="D151" s="4"/>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
-      <c r="J151" s="8"/>
-      <c r="K151" s="9"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="4"/>
       <c r="L151" s="1"/>
-      <c r="O151" s="10"/>
+      <c r="O151" s="4"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="9"/>
+      <c r="D152" s="4"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
-      <c r="J152" s="8"/>
-      <c r="K152" s="9"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="4"/>
       <c r="L152" s="1"/>
-      <c r="O152" s="10"/>
+      <c r="O152" s="4"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="9"/>
+      <c r="D153" s="4"/>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
-      <c r="J153" s="8"/>
-      <c r="K153" s="9"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="4"/>
       <c r="L153" s="1"/>
-      <c r="O153" s="10"/>
+      <c r="O153" s="4"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="9"/>
+      <c r="D154" s="4"/>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
-      <c r="J154" s="8"/>
-      <c r="K154" s="9"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="4"/>
       <c r="L154" s="1"/>
-      <c r="O154" s="10"/>
+      <c r="O154" s="4"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="9"/>
+      <c r="D155" s="4"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
-      <c r="J155" s="8"/>
-      <c r="K155" s="9"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="4"/>
       <c r="L155" s="1"/>
-      <c r="O155" s="10"/>
+      <c r="O155" s="4"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="9"/>
+      <c r="D156" s="4"/>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
-      <c r="J156" s="8"/>
-      <c r="K156" s="9"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="4"/>
       <c r="L156" s="1"/>
-      <c r="O156" s="10"/>
+      <c r="O156" s="4"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="9"/>
+      <c r="D157" s="4"/>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
-      <c r="J157" s="8"/>
-      <c r="K157" s="9"/>
+      <c r="J157" s="5"/>
+      <c r="K157" s="4"/>
       <c r="L157" s="1"/>
-      <c r="O157" s="10"/>
+      <c r="O157" s="4"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="9"/>
+      <c r="D158" s="4"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
-      <c r="J158" s="8"/>
-      <c r="K158" s="9"/>
+      <c r="J158" s="5"/>
+      <c r="K158" s="4"/>
       <c r="L158" s="1"/>
-      <c r="O158" s="10"/>
+      <c r="O158" s="4"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="9"/>
+      <c r="D159" s="4"/>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
-      <c r="J159" s="8"/>
-      <c r="K159" s="9"/>
+      <c r="J159" s="5"/>
+      <c r="K159" s="4"/>
       <c r="L159" s="1"/>
-      <c r="O159" s="10"/>
+      <c r="O159" s="4"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="9"/>
+      <c r="D160" s="4"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
-      <c r="J160" s="8"/>
-      <c r="K160" s="9"/>
+      <c r="J160" s="5"/>
+      <c r="K160" s="4"/>
       <c r="L160" s="1"/>
-      <c r="O160" s="10"/>
+      <c r="O160" s="4"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="9"/>
+      <c r="D161" s="4"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
-      <c r="J161" s="8"/>
-      <c r="K161" s="9"/>
+      <c r="J161" s="5"/>
+      <c r="K161" s="4"/>
       <c r="L161" s="1"/>
-      <c r="O161" s="10"/>
+      <c r="O161" s="4"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="9"/>
+      <c r="D162" s="4"/>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
-      <c r="J162" s="8"/>
-      <c r="K162" s="9"/>
+      <c r="J162" s="5"/>
+      <c r="K162" s="4"/>
       <c r="L162" s="1"/>
-      <c r="O162" s="10"/>
+      <c r="O162" s="4"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="9"/>
+      <c r="D163" s="4"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
-      <c r="J163" s="8"/>
-      <c r="K163" s="9"/>
+      <c r="J163" s="5"/>
+      <c r="K163" s="4"/>
       <c r="L163" s="1"/>
-      <c r="O163" s="10"/>
+      <c r="O163" s="4"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="9"/>
+      <c r="D164" s="4"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
-      <c r="J164" s="8"/>
-      <c r="K164" s="9"/>
+      <c r="J164" s="5"/>
+      <c r="K164" s="4"/>
       <c r="L164" s="1"/>
-      <c r="O164" s="10"/>
+      <c r="O164" s="4"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="9"/>
+      <c r="D165" s="4"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
-      <c r="J165" s="8"/>
-      <c r="K165" s="9"/>
+      <c r="J165" s="5"/>
+      <c r="K165" s="4"/>
       <c r="L165" s="1"/>
-      <c r="O165" s="10"/>
+      <c r="O165" s="4"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="9"/>
+      <c r="D166" s="4"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
-      <c r="J166" s="8"/>
-      <c r="K166" s="9"/>
+      <c r="J166" s="5"/>
+      <c r="K166" s="4"/>
       <c r="L166" s="1"/>
-      <c r="O166" s="10"/>
+      <c r="O166" s="4"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="9"/>
+      <c r="D167" s="4"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
-      <c r="J167" s="8"/>
-      <c r="K167" s="9"/>
+      <c r="J167" s="5"/>
+      <c r="K167" s="4"/>
       <c r="L167" s="1"/>
-      <c r="O167" s="10"/>
+      <c r="O167" s="4"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="9"/>
+      <c r="D168" s="4"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
-      <c r="J168" s="8"/>
-      <c r="K168" s="9"/>
+      <c r="J168" s="5"/>
+      <c r="K168" s="4"/>
       <c r="L168" s="1"/>
-      <c r="O168" s="10"/>
+      <c r="O168" s="4"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="9"/>
+      <c r="D169" s="4"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
-      <c r="J169" s="8"/>
-      <c r="K169" s="9"/>
+      <c r="J169" s="5"/>
+      <c r="K169" s="4"/>
       <c r="L169" s="1"/>
-      <c r="O169" s="10"/>
+      <c r="O169" s="4"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="9"/>
+      <c r="D170" s="4"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
-      <c r="J170" s="8"/>
-      <c r="K170" s="9"/>
+      <c r="J170" s="5"/>
+      <c r="K170" s="4"/>
       <c r="L170" s="1"/>
-      <c r="O170" s="10"/>
+      <c r="O170" s="4"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="9"/>
+      <c r="D171" s="4"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
-      <c r="J171" s="8"/>
-      <c r="K171" s="9"/>
+      <c r="J171" s="5"/>
+      <c r="K171" s="4"/>
       <c r="L171" s="1"/>
-      <c r="O171" s="10"/>
+      <c r="O171" s="4"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="9"/>
+      <c r="D172" s="4"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
-      <c r="J172" s="8"/>
-      <c r="K172" s="9"/>
+      <c r="J172" s="5"/>
+      <c r="K172" s="4"/>
       <c r="L172" s="1"/>
-      <c r="O172" s="10"/>
+      <c r="O172" s="4"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="9"/>
+      <c r="D173" s="4"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
-      <c r="J173" s="8"/>
-      <c r="K173" s="9"/>
+      <c r="J173" s="5"/>
+      <c r="K173" s="4"/>
       <c r="L173" s="1"/>
-      <c r="O173" s="10"/>
+      <c r="O173" s="4"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="9"/>
+      <c r="D174" s="4"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
-      <c r="J174" s="8"/>
-      <c r="K174" s="9"/>
+      <c r="J174" s="5"/>
+      <c r="K174" s="4"/>
       <c r="L174" s="1"/>
-      <c r="O174" s="10"/>
+      <c r="O174" s="4"/>
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="9"/>
+      <c r="D175" s="4"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
-      <c r="J175" s="8"/>
-      <c r="K175" s="9"/>
+      <c r="J175" s="5"/>
+      <c r="K175" s="4"/>
       <c r="L175" s="1"/>
-      <c r="O175" s="10"/>
+      <c r="O175" s="4"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="9"/>
+      <c r="D176" s="4"/>
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
-      <c r="J176" s="8"/>
-      <c r="K176" s="9"/>
+      <c r="J176" s="5"/>
+      <c r="K176" s="4"/>
       <c r="L176" s="1"/>
-      <c r="O176" s="10"/>
+      <c r="O176" s="4"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="9"/>
+      <c r="D177" s="4"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
-      <c r="J177" s="8"/>
-      <c r="K177" s="9"/>
+      <c r="J177" s="5"/>
+      <c r="K177" s="4"/>
       <c r="L177" s="1"/>
-      <c r="O177" s="10"/>
+      <c r="O177" s="4"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="9"/>
+      <c r="D178" s="4"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
-      <c r="J178" s="8"/>
-      <c r="K178" s="9"/>
+      <c r="J178" s="5"/>
+      <c r="K178" s="4"/>
       <c r="L178" s="1"/>
-      <c r="O178" s="10"/>
+      <c r="O178" s="4"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="9"/>
+      <c r="D179" s="4"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
-      <c r="J179" s="8"/>
-      <c r="K179" s="9"/>
+      <c r="J179" s="5"/>
+      <c r="K179" s="4"/>
       <c r="L179" s="1"/>
-      <c r="O179" s="10"/>
+      <c r="O179" s="4"/>
     </row>
     <row r="180" ht="14.25" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="9"/>
+      <c r="D180" s="4"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
-      <c r="J180" s="8"/>
-      <c r="K180" s="9"/>
+      <c r="J180" s="5"/>
+      <c r="K180" s="4"/>
       <c r="L180" s="1"/>
-      <c r="O180" s="10"/>
+      <c r="O180" s="4"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="9"/>
+      <c r="D181" s="4"/>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
-      <c r="J181" s="8"/>
-      <c r="K181" s="9"/>
+      <c r="J181" s="5"/>
+      <c r="K181" s="4"/>
       <c r="L181" s="1"/>
-      <c r="O181" s="10"/>
+      <c r="O181" s="4"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="9"/>
+      <c r="D182" s="4"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
-      <c r="J182" s="8"/>
-      <c r="K182" s="9"/>
+      <c r="J182" s="5"/>
+      <c r="K182" s="4"/>
       <c r="L182" s="1"/>
-      <c r="O182" s="10"/>
+      <c r="O182" s="4"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="9"/>
+      <c r="D183" s="4"/>
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
-      <c r="J183" s="8"/>
-      <c r="K183" s="9"/>
+      <c r="J183" s="5"/>
+      <c r="K183" s="4"/>
       <c r="L183" s="1"/>
-      <c r="O183" s="10"/>
+      <c r="O183" s="4"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="9"/>
+      <c r="D184" s="4"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
-      <c r="J184" s="8"/>
-      <c r="K184" s="9"/>
+      <c r="J184" s="5"/>
+      <c r="K184" s="4"/>
       <c r="L184" s="1"/>
-      <c r="O184" s="10"/>
+      <c r="O184" s="4"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="9"/>
+      <c r="D185" s="4"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
-      <c r="J185" s="8"/>
-      <c r="K185" s="9"/>
+      <c r="J185" s="5"/>
+      <c r="K185" s="4"/>
       <c r="L185" s="1"/>
-      <c r="O185" s="10"/>
+      <c r="O185" s="4"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="9"/>
+      <c r="D186" s="4"/>
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
       <c r="H186" s="1"/>
-      <c r="J186" s="8"/>
-      <c r="K186" s="9"/>
+      <c r="J186" s="5"/>
+      <c r="K186" s="4"/>
       <c r="L186" s="1"/>
-      <c r="O186" s="10"/>
+      <c r="O186" s="4"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="9"/>
+      <c r="D187" s="4"/>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
-      <c r="J187" s="8"/>
-      <c r="K187" s="9"/>
+      <c r="J187" s="5"/>
+      <c r="K187" s="4"/>
       <c r="L187" s="1"/>
-      <c r="O187" s="10"/>
+      <c r="O187" s="4"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="9"/>
+      <c r="D188" s="4"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
-      <c r="J188" s="8"/>
-      <c r="K188" s="9"/>
+      <c r="J188" s="5"/>
+      <c r="K188" s="4"/>
       <c r="L188" s="1"/>
-      <c r="O188" s="10"/>
+      <c r="O188" s="4"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="9"/>
+      <c r="D189" s="4"/>
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
-      <c r="J189" s="8"/>
-      <c r="K189" s="9"/>
+      <c r="J189" s="5"/>
+      <c r="K189" s="4"/>
       <c r="L189" s="1"/>
-      <c r="O189" s="10"/>
+      <c r="O189" s="4"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="9"/>
+      <c r="D190" s="4"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
-      <c r="J190" s="8"/>
-      <c r="K190" s="9"/>
+      <c r="J190" s="5"/>
+      <c r="K190" s="4"/>
       <c r="L190" s="1"/>
-      <c r="O190" s="10"/>
+      <c r="O190" s="4"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="9"/>
+      <c r="D191" s="4"/>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
-      <c r="J191" s="8"/>
-      <c r="K191" s="9"/>
+      <c r="J191" s="5"/>
+      <c r="K191" s="4"/>
       <c r="L191" s="1"/>
-      <c r="O191" s="10"/>
+      <c r="O191" s="4"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="9"/>
+      <c r="D192" s="4"/>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
       <c r="H192" s="1"/>
-      <c r="J192" s="8"/>
-      <c r="K192" s="9"/>
+      <c r="J192" s="5"/>
+      <c r="K192" s="4"/>
       <c r="L192" s="1"/>
-      <c r="O192" s="10"/>
+      <c r="O192" s="4"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="9"/>
+      <c r="D193" s="4"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
-      <c r="J193" s="8"/>
-      <c r="K193" s="9"/>
+      <c r="J193" s="5"/>
+      <c r="K193" s="4"/>
       <c r="L193" s="1"/>
-      <c r="O193" s="10"/>
+      <c r="O193" s="4"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="9"/>
+      <c r="D194" s="4"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
-      <c r="J194" s="8"/>
-      <c r="K194" s="9"/>
+      <c r="J194" s="5"/>
+      <c r="K194" s="4"/>
       <c r="L194" s="1"/>
-      <c r="O194" s="10"/>
+      <c r="O194" s="4"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="9"/>
+      <c r="D195" s="4"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
-      <c r="J195" s="8"/>
-      <c r="K195" s="9"/>
+      <c r="J195" s="5"/>
+      <c r="K195" s="4"/>
       <c r="L195" s="1"/>
-      <c r="O195" s="10"/>
+      <c r="O195" s="4"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="9"/>
+      <c r="D196" s="4"/>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
-      <c r="J196" s="8"/>
-      <c r="K196" s="9"/>
+      <c r="J196" s="5"/>
+      <c r="K196" s="4"/>
       <c r="L196" s="1"/>
-      <c r="O196" s="10"/>
+      <c r="O196" s="4"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="9"/>
+      <c r="D197" s="4"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
-      <c r="J197" s="8"/>
-      <c r="K197" s="9"/>
+      <c r="J197" s="5"/>
+      <c r="K197" s="4"/>
       <c r="L197" s="1"/>
-      <c r="O197" s="10"/>
+      <c r="O197" s="4"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="9"/>
+      <c r="D198" s="4"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
-      <c r="J198" s="8"/>
-      <c r="K198" s="9"/>
+      <c r="J198" s="5"/>
+      <c r="K198" s="4"/>
       <c r="L198" s="1"/>
-      <c r="O198" s="10"/>
+      <c r="O198" s="4"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="9"/>
+      <c r="D199" s="4"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
-      <c r="J199" s="8"/>
-      <c r="K199" s="9"/>
+      <c r="J199" s="5"/>
+      <c r="K199" s="4"/>
       <c r="L199" s="1"/>
-      <c r="O199" s="10"/>
+      <c r="O199" s="4"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="9"/>
+      <c r="D200" s="4"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
-      <c r="J200" s="8"/>
-      <c r="K200" s="9"/>
+      <c r="J200" s="5"/>
+      <c r="K200" s="4"/>
       <c r="L200" s="1"/>
-      <c r="O200" s="10"/>
+      <c r="O200" s="4"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="9"/>
+      <c r="D201" s="4"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
-      <c r="J201" s="8"/>
-      <c r="K201" s="9"/>
+      <c r="J201" s="5"/>
+      <c r="K201" s="4"/>
       <c r="L201" s="1"/>
-      <c r="O201" s="10"/>
+      <c r="O201" s="4"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="9"/>
+      <c r="D202" s="4"/>
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
-      <c r="J202" s="8"/>
-      <c r="K202" s="9"/>
+      <c r="J202" s="5"/>
+      <c r="K202" s="4"/>
       <c r="L202" s="1"/>
-      <c r="O202" s="10"/>
+      <c r="O202" s="4"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="9"/>
+      <c r="D203" s="4"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
-      <c r="J203" s="8"/>
-      <c r="K203" s="9"/>
+      <c r="J203" s="5"/>
+      <c r="K203" s="4"/>
       <c r="L203" s="1"/>
-      <c r="O203" s="10"/>
+      <c r="O203" s="4"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="9"/>
+      <c r="D204" s="4"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
-      <c r="J204" s="8"/>
-      <c r="K204" s="9"/>
+      <c r="J204" s="5"/>
+      <c r="K204" s="4"/>
       <c r="L204" s="1"/>
-      <c r="O204" s="10"/>
+      <c r="O204" s="4"/>
     </row>
     <row r="205" ht="14.25" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="2"/>
-      <c r="D205" s="9"/>
+      <c r="D205" s="4"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
-      <c r="J205" s="8"/>
-      <c r="K205" s="9"/>
+      <c r="J205" s="5"/>
+      <c r="K205" s="4"/>
       <c r="L205" s="1"/>
-      <c r="O205" s="10"/>
+      <c r="O205" s="4"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="2"/>
-      <c r="D206" s="9"/>
+      <c r="D206" s="4"/>
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
-      <c r="J206" s="8"/>
-      <c r="K206" s="9"/>
+      <c r="J206" s="5"/>
+      <c r="K206" s="4"/>
       <c r="L206" s="1"/>
-      <c r="O206" s="10"/>
+      <c r="O206" s="4"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="2"/>
-      <c r="D207" s="9"/>
+      <c r="D207" s="4"/>
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
-      <c r="J207" s="8"/>
-      <c r="K207" s="9"/>
+      <c r="J207" s="5"/>
+      <c r="K207" s="4"/>
       <c r="L207" s="1"/>
-      <c r="O207" s="10"/>
+      <c r="O207" s="4"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="2"/>
-      <c r="D208" s="9"/>
+      <c r="D208" s="4"/>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
-      <c r="J208" s="8"/>
-      <c r="K208" s="9"/>
+      <c r="J208" s="5"/>
+      <c r="K208" s="4"/>
       <c r="L208" s="1"/>
-      <c r="O208" s="10"/>
+      <c r="O208" s="4"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="2"/>
-      <c r="D209" s="9"/>
+      <c r="D209" s="4"/>
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
-      <c r="J209" s="8"/>
-      <c r="K209" s="9"/>
+      <c r="J209" s="5"/>
+      <c r="K209" s="4"/>
       <c r="L209" s="1"/>
-      <c r="O209" s="10"/>
+      <c r="O209" s="4"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="2"/>
-      <c r="D210" s="9"/>
+      <c r="D210" s="4"/>
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
-      <c r="J210" s="8"/>
-      <c r="K210" s="9"/>
+      <c r="J210" s="5"/>
+      <c r="K210" s="4"/>
       <c r="L210" s="1"/>
-      <c r="O210" s="10"/>
+      <c r="O210" s="4"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="2"/>
-      <c r="D211" s="9"/>
+      <c r="D211" s="4"/>
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
-      <c r="J211" s="8"/>
-      <c r="K211" s="9"/>
+      <c r="J211" s="5"/>
+      <c r="K211" s="4"/>
       <c r="L211" s="1"/>
-      <c r="O211" s="10"/>
+      <c r="O211" s="4"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="2"/>
-      <c r="D212" s="9"/>
+      <c r="D212" s="4"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
-      <c r="J212" s="8"/>
-      <c r="K212" s="9"/>
+      <c r="J212" s="5"/>
+      <c r="K212" s="4"/>
       <c r="L212" s="1"/>
-      <c r="O212" s="10"/>
+      <c r="O212" s="4"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="2"/>
-      <c r="D213" s="9"/>
+      <c r="D213" s="4"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
-      <c r="J213" s="8"/>
-      <c r="K213" s="9"/>
+      <c r="J213" s="5"/>
+      <c r="K213" s="4"/>
       <c r="L213" s="1"/>
-      <c r="O213" s="10"/>
+      <c r="O213" s="4"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="2"/>
-      <c r="D214" s="9"/>
+      <c r="D214" s="4"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
       <c r="H214" s="1"/>
-      <c r="J214" s="8"/>
-      <c r="K214" s="9"/>
+      <c r="J214" s="5"/>
+      <c r="K214" s="4"/>
       <c r="L214" s="1"/>
-      <c r="O214" s="10"/>
+      <c r="O214" s="4"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="2"/>
-      <c r="D215" s="9"/>
+      <c r="D215" s="4"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
-      <c r="J215" s="8"/>
-      <c r="K215" s="9"/>
+      <c r="J215" s="5"/>
+      <c r="K215" s="4"/>
       <c r="L215" s="1"/>
-      <c r="O215" s="10"/>
+      <c r="O215" s="4"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="9"/>
+      <c r="D216" s="4"/>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
-      <c r="J216" s="8"/>
-      <c r="K216" s="9"/>
+      <c r="J216" s="5"/>
+      <c r="K216" s="4"/>
       <c r="L216" s="1"/>
-      <c r="O216" s="10"/>
+      <c r="O216" s="4"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="2"/>
-      <c r="D217" s="9"/>
+      <c r="D217" s="4"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1"/>
-      <c r="J217" s="8"/>
-      <c r="K217" s="9"/>
+      <c r="J217" s="5"/>
+      <c r="K217" s="4"/>
       <c r="L217" s="1"/>
-      <c r="O217" s="10"/>
+      <c r="O217" s="4"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="2"/>
-      <c r="D218" s="9"/>
+      <c r="D218" s="4"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1"/>
-      <c r="J218" s="8"/>
-      <c r="K218" s="9"/>
+      <c r="J218" s="5"/>
+      <c r="K218" s="4"/>
       <c r="L218" s="1"/>
-      <c r="O218" s="10"/>
+      <c r="O218" s="4"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="2"/>
-      <c r="D219" s="9"/>
+      <c r="D219" s="4"/>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
       <c r="H219" s="1"/>
-      <c r="J219" s="8"/>
-      <c r="K219" s="9"/>
+      <c r="J219" s="5"/>
+      <c r="K219" s="4"/>
       <c r="L219" s="1"/>
-      <c r="O219" s="10"/>
+      <c r="O219" s="4"/>
     </row>
     <row r="220" ht="14.25" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="2"/>
-      <c r="D220" s="9"/>
+      <c r="D220" s="4"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
       <c r="H220" s="1"/>
-      <c r="J220" s="8"/>
-      <c r="K220" s="9"/>
+      <c r="J220" s="5"/>
+      <c r="K220" s="4"/>
       <c r="L220" s="1"/>
-      <c r="O220" s="10"/>
+      <c r="O220" s="4"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="2"/>
-      <c r="D221" s="9"/>
+      <c r="D221" s="4"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
       <c r="H221" s="1"/>
-      <c r="J221" s="8"/>
-      <c r="K221" s="9"/>
+      <c r="J221" s="5"/>
+      <c r="K221" s="4"/>
       <c r="L221" s="1"/>
-      <c r="O221" s="10"/>
+      <c r="O221" s="4"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="2"/>
-      <c r="D222" s="9"/>
+      <c r="D222" s="4"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
-      <c r="J222" s="8"/>
-      <c r="K222" s="9"/>
+      <c r="J222" s="5"/>
+      <c r="K222" s="4"/>
       <c r="L222" s="1"/>
-      <c r="O222" s="10"/>
+      <c r="O222" s="4"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="2"/>
-      <c r="D223" s="9"/>
+      <c r="D223" s="4"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
-      <c r="J223" s="8"/>
-      <c r="K223" s="9"/>
+      <c r="J223" s="5"/>
+      <c r="K223" s="4"/>
       <c r="L223" s="1"/>
-      <c r="O223" s="10"/>
+      <c r="O223" s="4"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="2"/>
-      <c r="D224" s="9"/>
+      <c r="D224" s="4"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
-      <c r="J224" s="8"/>
-      <c r="K224" s="9"/>
+      <c r="J224" s="5"/>
+      <c r="K224" s="4"/>
       <c r="L224" s="1"/>
-      <c r="O224" s="10"/>
+      <c r="O224" s="4"/>
     </row>
     <row r="225" ht="14.25" customHeight="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="2"/>
-      <c r="D225" s="9"/>
+      <c r="D225" s="4"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
-      <c r="J225" s="8"/>
-      <c r="K225" s="9"/>
+      <c r="J225" s="5"/>
+      <c r="K225" s="4"/>
       <c r="L225" s="1"/>
-      <c r="O225" s="10"/>
+      <c r="O225" s="4"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="2"/>
-      <c r="D226" s="9"/>
+      <c r="D226" s="4"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
       <c r="H226" s="1"/>
-      <c r="J226" s="8"/>
-      <c r="K226" s="9"/>
+      <c r="J226" s="5"/>
+      <c r="K226" s="4"/>
       <c r="L226" s="1"/>
-      <c r="O226" s="10"/>
+      <c r="O226" s="4"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="2"/>
-      <c r="D227" s="9"/>
+      <c r="D227" s="4"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
       <c r="H227" s="1"/>
-      <c r="J227" s="8"/>
-      <c r="K227" s="9"/>
+      <c r="J227" s="5"/>
+      <c r="K227" s="4"/>
       <c r="L227" s="1"/>
-      <c r="O227" s="10"/>
+      <c r="O227" s="4"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="2"/>
-      <c r="D228" s="9"/>
+      <c r="D228" s="4"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
-      <c r="J228" s="8"/>
-      <c r="K228" s="9"/>
+      <c r="J228" s="5"/>
+      <c r="K228" s="4"/>
       <c r="L228" s="1"/>
-      <c r="O228" s="10"/>
+      <c r="O228" s="4"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="2"/>
-      <c r="D229" s="9"/>
+      <c r="D229" s="4"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
       <c r="H229" s="1"/>
-      <c r="J229" s="8"/>
-      <c r="K229" s="9"/>
+      <c r="J229" s="5"/>
+      <c r="K229" s="4"/>
       <c r="L229" s="1"/>
-      <c r="O229" s="10"/>
+      <c r="O229" s="4"/>
     </row>
     <row r="230" ht="14.25" customHeight="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="2"/>
-      <c r="D230" s="9"/>
+      <c r="D230" s="4"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
-      <c r="J230" s="8"/>
-      <c r="K230" s="9"/>
+      <c r="J230" s="5"/>
+      <c r="K230" s="4"/>
       <c r="L230" s="1"/>
-      <c r="O230" s="10"/>
+      <c r="O230" s="4"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="2"/>
-      <c r="D231" s="9"/>
+      <c r="D231" s="4"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
       <c r="H231" s="1"/>
-      <c r="J231" s="8"/>
-      <c r="K231" s="9"/>
+      <c r="J231" s="5"/>
+      <c r="K231" s="4"/>
       <c r="L231" s="1"/>
-      <c r="O231" s="10"/>
+      <c r="O231" s="4"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="2"/>
-      <c r="D232" s="9"/>
+      <c r="D232" s="4"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
-      <c r="J232" s="8"/>
-      <c r="K232" s="9"/>
+      <c r="J232" s="5"/>
+      <c r="K232" s="4"/>
       <c r="L232" s="1"/>
-      <c r="O232" s="10"/>
+      <c r="O232" s="4"/>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="2"/>
-      <c r="D233" s="9"/>
+      <c r="D233" s="4"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
-      <c r="J233" s="8"/>
-      <c r="K233" s="9"/>
+      <c r="J233" s="5"/>
+      <c r="K233" s="4"/>
       <c r="L233" s="1"/>
-      <c r="O233" s="10"/>
+      <c r="O233" s="4"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="2"/>
-      <c r="D234" s="9"/>
+      <c r="D234" s="4"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
-      <c r="J234" s="8"/>
-      <c r="K234" s="9"/>
+      <c r="J234" s="5"/>
+      <c r="K234" s="4"/>
       <c r="L234" s="1"/>
-      <c r="O234" s="10"/>
+      <c r="O234" s="4"/>
     </row>
     <row r="235" ht="14.25" customHeight="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="2"/>
-      <c r="D235" s="9"/>
+      <c r="D235" s="4"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
-      <c r="J235" s="8"/>
-      <c r="K235" s="9"/>
+      <c r="J235" s="5"/>
+      <c r="K235" s="4"/>
       <c r="L235" s="1"/>
-      <c r="O235" s="10"/>
+      <c r="O235" s="4"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="2"/>
-      <c r="D236" s="9"/>
+      <c r="D236" s="4"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
-      <c r="J236" s="8"/>
-      <c r="K236" s="9"/>
+      <c r="J236" s="5"/>
+      <c r="K236" s="4"/>
       <c r="L236" s="1"/>
-      <c r="O236" s="10"/>
+      <c r="O236" s="4"/>
     </row>
     <row r="237" ht="15.75" customHeight="1"/>
     <row r="238" ht="15.75" customHeight="1"/>
@@ -5361,11 +5537,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
-    <row r="1005" ht="15.75" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A1 A15:A18 A20:A21 A27:A28 A35:A36">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -5425,16 +5596,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1"/>
@@ -5456,16 +5627,16 @@
       <c r="U1" s="1"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -5487,16 +5658,16 @@
       <c r="U2" s="1"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>106</v>
       </c>
       <c r="E3" s="1"/>
@@ -5519,9 +5690,9 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -5542,9 +5713,9 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -5565,9 +5736,9 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -5588,9 +5759,9 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -5611,9 +5782,9 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -5634,9 +5805,9 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="30"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="9"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -5657,9 +5828,9 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -5679,10 +5850,10 @@
       <c r="U10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="9"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="9"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -5702,10 +5873,10 @@
       <c r="U11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="9"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -5725,10 +5896,10 @@
       <c r="U12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="9"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="9"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -5748,10 +5919,10 @@
       <c r="U13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="9"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -5771,10 +5942,10 @@
       <c r="U14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="9"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -5794,10 +5965,10 @@
       <c r="U15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="9"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5817,10 +5988,10 @@
       <c r="U16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="9"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -5840,10 +6011,10 @@
       <c r="U17" s="1"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="9"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -5863,10 +6034,10 @@
       <c r="U18" s="1"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="9"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -5889,7 +6060,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="9"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -5912,7 +6083,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="4"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -5935,7 +6106,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="4"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -5958,7 +6129,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="9"/>
+      <c r="D23" s="4"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -5981,7 +6152,7 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="9"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -6004,7 +6175,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="9"/>
+      <c r="D25" s="4"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -6027,7 +6198,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="9"/>
+      <c r="D26" s="4"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -6050,7 +6221,7 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="9"/>
+      <c r="D27" s="4"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -6073,7 +6244,7 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="9"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -6096,7 +6267,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="9"/>
+      <c r="D29" s="4"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -6119,7 +6290,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="4"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -6142,7 +6313,7 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="4"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -6165,7 +6336,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
-      <c r="D32" s="9"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -6188,7 +6359,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="9"/>
+      <c r="D33" s="4"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -6211,7 +6382,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="9"/>
+      <c r="D34" s="4"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -6234,7 +6405,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="9"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -6257,7 +6428,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="9"/>
+      <c r="D36" s="4"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -6280,7 +6451,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="9"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -6303,7 +6474,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="9"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -6326,7 +6497,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="9"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -6349,7 +6520,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="9"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -6372,7 +6543,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="9"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -6395,7 +6566,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="9"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -6418,7 +6589,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="9"/>
+      <c r="D43" s="4"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -6441,7 +6612,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="9"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -6464,7 +6635,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="9"/>
+      <c r="D45" s="4"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -6487,7 +6658,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="9"/>
+      <c r="D46" s="4"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -6510,7 +6681,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="9"/>
+      <c r="D47" s="4"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -6533,7 +6704,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="9"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -6556,7 +6727,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="9"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -6579,7 +6750,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="9"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -6602,7 +6773,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="9"/>
+      <c r="D51" s="4"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -6625,7 +6796,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="9"/>
+      <c r="D52" s="4"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -6648,7 +6819,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="9"/>
+      <c r="D53" s="4"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -6671,7 +6842,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="9"/>
+      <c r="D54" s="4"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -6694,7 +6865,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="9"/>
+      <c r="D55" s="4"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -6717,7 +6888,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
-      <c r="D56" s="9"/>
+      <c r="D56" s="4"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -6740,7 +6911,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="9"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -6763,7 +6934,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="9"/>
+      <c r="D58" s="4"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -6786,7 +6957,7 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="9"/>
+      <c r="D59" s="4"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -6809,7 +6980,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="9"/>
+      <c r="D60" s="4"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -6832,7 +7003,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="4"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -6855,7 +7026,7 @@
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="9"/>
+      <c r="D62" s="4"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -6878,7 +7049,7 @@
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="9"/>
+      <c r="D63" s="4"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -6901,7 +7072,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="9"/>
+      <c r="D64" s="4"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -6924,7 +7095,7 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
-      <c r="D65" s="9"/>
+      <c r="D65" s="4"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -6947,7 +7118,7 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="4"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -6970,7 +7141,7 @@
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="4"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -6993,7 +7164,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="4"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -7016,7 +7187,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
-      <c r="D69" s="9"/>
+      <c r="D69" s="4"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -7039,7 +7210,7 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
-      <c r="D70" s="9"/>
+      <c r="D70" s="4"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -7062,7 +7233,7 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
-      <c r="D71" s="9"/>
+      <c r="D71" s="4"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -7085,7 +7256,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
-      <c r="D72" s="9"/>
+      <c r="D72" s="4"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -7108,7 +7279,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
-      <c r="D73" s="9"/>
+      <c r="D73" s="4"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -7131,7 +7302,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="9"/>
+      <c r="D74" s="4"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -7154,7 +7325,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="9"/>
+      <c r="D75" s="4"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -7177,7 +7348,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="9"/>
+      <c r="D76" s="4"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -7200,7 +7371,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="9"/>
+      <c r="D77" s="4"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -7223,7 +7394,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="9"/>
+      <c r="D78" s="4"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -7246,7 +7417,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
-      <c r="D79" s="9"/>
+      <c r="D79" s="4"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -7269,7 +7440,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
-      <c r="D80" s="9"/>
+      <c r="D80" s="4"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -7292,7 +7463,7 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
-      <c r="D81" s="9"/>
+      <c r="D81" s="4"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -7315,7 +7486,7 @@
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
-      <c r="D82" s="9"/>
+      <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
@@ -7338,7 +7509,7 @@
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
-      <c r="D83" s="9"/>
+      <c r="D83" s="4"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
@@ -7361,7 +7532,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
-      <c r="D84" s="9"/>
+      <c r="D84" s="4"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
@@ -7384,7 +7555,7 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
-      <c r="D85" s="9"/>
+      <c r="D85" s="4"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
@@ -7407,7 +7578,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
-      <c r="D86" s="9"/>
+      <c r="D86" s="4"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
@@ -7430,7 +7601,7 @@
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
-      <c r="D87" s="9"/>
+      <c r="D87" s="4"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
@@ -7453,7 +7624,7 @@
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
-      <c r="D88" s="9"/>
+      <c r="D88" s="4"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
@@ -7476,7 +7647,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="D89" s="9"/>
+      <c r="D89" s="4"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -7499,7 +7670,7 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
-      <c r="D90" s="9"/>
+      <c r="D90" s="4"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
@@ -7522,7 +7693,7 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
-      <c r="D91" s="9"/>
+      <c r="D91" s="4"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
@@ -7545,7 +7716,7 @@
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
-      <c r="D92" s="9"/>
+      <c r="D92" s="4"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
@@ -7568,7 +7739,7 @@
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
-      <c r="D93" s="9"/>
+      <c r="D93" s="4"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
@@ -7591,7 +7762,7 @@
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="9"/>
+      <c r="D94" s="4"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -7614,7 +7785,7 @@
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
-      <c r="D95" s="9"/>
+      <c r="D95" s="4"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
@@ -7637,7 +7808,7 @@
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
-      <c r="D96" s="9"/>
+      <c r="D96" s="4"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
@@ -7660,7 +7831,7 @@
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
-      <c r="D97" s="9"/>
+      <c r="D97" s="4"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
@@ -7683,7 +7854,7 @@
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
-      <c r="D98" s="9"/>
+      <c r="D98" s="4"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
@@ -7706,7 +7877,7 @@
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
-      <c r="D99" s="9"/>
+      <c r="D99" s="4"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -7729,7 +7900,7 @@
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
-      <c r="D100" s="9"/>
+      <c r="D100" s="4"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
@@ -7752,7 +7923,7 @@
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
-      <c r="D101" s="9"/>
+      <c r="D101" s="4"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -7775,7 +7946,7 @@
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
-      <c r="D102" s="9"/>
+      <c r="D102" s="4"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
@@ -7798,7 +7969,7 @@
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
-      <c r="D103" s="9"/>
+      <c r="D103" s="4"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -7821,7 +7992,7 @@
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
-      <c r="D104" s="9"/>
+      <c r="D104" s="4"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
@@ -7844,7 +8015,7 @@
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
-      <c r="D105" s="9"/>
+      <c r="D105" s="4"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
@@ -7867,7 +8038,7 @@
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
-      <c r="D106" s="9"/>
+      <c r="D106" s="4"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
@@ -7890,7 +8061,7 @@
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
-      <c r="D107" s="9"/>
+      <c r="D107" s="4"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -7913,7 +8084,7 @@
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
-      <c r="D108" s="9"/>
+      <c r="D108" s="4"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -7936,7 +8107,7 @@
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
-      <c r="D109" s="9"/>
+      <c r="D109" s="4"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
@@ -7959,7 +8130,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
-      <c r="D110" s="9"/>
+      <c r="D110" s="4"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
@@ -7982,7 +8153,7 @@
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
-      <c r="D111" s="9"/>
+      <c r="D111" s="4"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
@@ -8005,7 +8176,7 @@
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
-      <c r="D112" s="9"/>
+      <c r="D112" s="4"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
@@ -8028,7 +8199,7 @@
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
-      <c r="D113" s="9"/>
+      <c r="D113" s="4"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
@@ -8051,7 +8222,7 @@
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
-      <c r="D114" s="9"/>
+      <c r="D114" s="4"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
@@ -8074,7 +8245,7 @@
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
-      <c r="D115" s="9"/>
+      <c r="D115" s="4"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -8097,7 +8268,7 @@
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
-      <c r="D116" s="9"/>
+      <c r="D116" s="4"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
@@ -8120,7 +8291,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
-      <c r="D117" s="9"/>
+      <c r="D117" s="4"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
@@ -8143,7 +8314,7 @@
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
-      <c r="D118" s="9"/>
+      <c r="D118" s="4"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
@@ -8166,7 +8337,7 @@
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
-      <c r="D119" s="9"/>
+      <c r="D119" s="4"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
@@ -8189,7 +8360,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
-      <c r="D120" s="9"/>
+      <c r="D120" s="4"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
@@ -8212,7 +8383,7 @@
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
-      <c r="D121" s="9"/>
+      <c r="D121" s="4"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -8235,7 +8406,7 @@
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
-      <c r="D122" s="9"/>
+      <c r="D122" s="4"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
@@ -8258,7 +8429,7 @@
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
-      <c r="D123" s="9"/>
+      <c r="D123" s="4"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -8281,7 +8452,7 @@
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
-      <c r="D124" s="9"/>
+      <c r="D124" s="4"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -8304,7 +8475,7 @@
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
-      <c r="D125" s="9"/>
+      <c r="D125" s="4"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
@@ -8327,7 +8498,7 @@
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
-      <c r="D126" s="9"/>
+      <c r="D126" s="4"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
@@ -8350,7 +8521,7 @@
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
-      <c r="D127" s="9"/>
+      <c r="D127" s="4"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
@@ -8373,7 +8544,7 @@
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
-      <c r="D128" s="9"/>
+      <c r="D128" s="4"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
@@ -8396,7 +8567,7 @@
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
-      <c r="D129" s="9"/>
+      <c r="D129" s="4"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
@@ -8419,7 +8590,7 @@
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
-      <c r="D130" s="9"/>
+      <c r="D130" s="4"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
@@ -8442,7 +8613,7 @@
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
-      <c r="D131" s="9"/>
+      <c r="D131" s="4"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
@@ -8465,7 +8636,7 @@
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
-      <c r="D132" s="9"/>
+      <c r="D132" s="4"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
@@ -8488,7 +8659,7 @@
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
-      <c r="D133" s="9"/>
+      <c r="D133" s="4"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
@@ -8511,7 +8682,7 @@
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
-      <c r="D134" s="9"/>
+      <c r="D134" s="4"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -8534,7 +8705,7 @@
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
-      <c r="D135" s="9"/>
+      <c r="D135" s="4"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -8557,7 +8728,7 @@
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
-      <c r="D136" s="9"/>
+      <c r="D136" s="4"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
@@ -8580,7 +8751,7 @@
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
-      <c r="D137" s="9"/>
+      <c r="D137" s="4"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -8603,7 +8774,7 @@
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
-      <c r="D138" s="9"/>
+      <c r="D138" s="4"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
@@ -8626,7 +8797,7 @@
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
-      <c r="D139" s="9"/>
+      <c r="D139" s="4"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
@@ -8649,7 +8820,7 @@
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
-      <c r="D140" s="9"/>
+      <c r="D140" s="4"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
@@ -8672,7 +8843,7 @@
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
-      <c r="D141" s="9"/>
+      <c r="D141" s="4"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
@@ -8695,7 +8866,7 @@
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
-      <c r="D142" s="9"/>
+      <c r="D142" s="4"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
@@ -8718,7 +8889,7 @@
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
-      <c r="D143" s="9"/>
+      <c r="D143" s="4"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
@@ -8741,7 +8912,7 @@
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
-      <c r="D144" s="9"/>
+      <c r="D144" s="4"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
@@ -8764,7 +8935,7 @@
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
-      <c r="D145" s="9"/>
+      <c r="D145" s="4"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
@@ -8787,7 +8958,7 @@
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
-      <c r="D146" s="9"/>
+      <c r="D146" s="4"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
@@ -8810,7 +8981,7 @@
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
-      <c r="D147" s="9"/>
+      <c r="D147" s="4"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
@@ -8833,7 +9004,7 @@
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
-      <c r="D148" s="9"/>
+      <c r="D148" s="4"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
@@ -8856,7 +9027,7 @@
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
-      <c r="D149" s="9"/>
+      <c r="D149" s="4"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
@@ -8879,7 +9050,7 @@
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
-      <c r="D150" s="9"/>
+      <c r="D150" s="4"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
@@ -8902,7 +9073,7 @@
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
-      <c r="D151" s="9"/>
+      <c r="D151" s="4"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
@@ -8925,7 +9096,7 @@
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
-      <c r="D152" s="9"/>
+      <c r="D152" s="4"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
@@ -8948,7 +9119,7 @@
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
-      <c r="D153" s="9"/>
+      <c r="D153" s="4"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
@@ -8971,7 +9142,7 @@
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
-      <c r="D154" s="9"/>
+      <c r="D154" s="4"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
@@ -8994,7 +9165,7 @@
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
-      <c r="D155" s="9"/>
+      <c r="D155" s="4"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -9017,7 +9188,7 @@
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
-      <c r="D156" s="9"/>
+      <c r="D156" s="4"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
@@ -9040,7 +9211,7 @@
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
-      <c r="D157" s="9"/>
+      <c r="D157" s="4"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
@@ -9063,7 +9234,7 @@
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
-      <c r="D158" s="9"/>
+      <c r="D158" s="4"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
@@ -9086,7 +9257,7 @@
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
-      <c r="D159" s="9"/>
+      <c r="D159" s="4"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
@@ -9109,7 +9280,7 @@
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
-      <c r="D160" s="9"/>
+      <c r="D160" s="4"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
@@ -9132,7 +9303,7 @@
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
-      <c r="D161" s="9"/>
+      <c r="D161" s="4"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
@@ -9155,7 +9326,7 @@
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
-      <c r="D162" s="9"/>
+      <c r="D162" s="4"/>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
@@ -9178,7 +9349,7 @@
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
-      <c r="D163" s="9"/>
+      <c r="D163" s="4"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
@@ -9201,7 +9372,7 @@
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
-      <c r="D164" s="9"/>
+      <c r="D164" s="4"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
@@ -9224,7 +9395,7 @@
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
-      <c r="D165" s="9"/>
+      <c r="D165" s="4"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -9247,7 +9418,7 @@
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
-      <c r="D166" s="9"/>
+      <c r="D166" s="4"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
@@ -9270,7 +9441,7 @@
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
-      <c r="D167" s="9"/>
+      <c r="D167" s="4"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
@@ -9293,7 +9464,7 @@
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
-      <c r="D168" s="9"/>
+      <c r="D168" s="4"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
@@ -9316,7 +9487,7 @@
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
-      <c r="D169" s="9"/>
+      <c r="D169" s="4"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
@@ -9339,7 +9510,7 @@
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
-      <c r="D170" s="9"/>
+      <c r="D170" s="4"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
@@ -9362,7 +9533,7 @@
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
-      <c r="D171" s="9"/>
+      <c r="D171" s="4"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
@@ -9385,7 +9556,7 @@
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
-      <c r="D172" s="9"/>
+      <c r="D172" s="4"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
@@ -9408,7 +9579,7 @@
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="9"/>
+      <c r="D173" s="4"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
@@ -9431,7 +9602,7 @@
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
-      <c r="D174" s="9"/>
+      <c r="D174" s="4"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
@@ -9454,7 +9625,7 @@
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="9"/>
+      <c r="D175" s="4"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
@@ -9477,7 +9648,7 @@
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
-      <c r="D176" s="9"/>
+      <c r="D176" s="4"/>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
@@ -9500,7 +9671,7 @@
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
-      <c r="D177" s="9"/>
+      <c r="D177" s="4"/>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
@@ -9523,7 +9694,7 @@
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
-      <c r="D178" s="9"/>
+      <c r="D178" s="4"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
@@ -9546,7 +9717,7 @@
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
-      <c r="D179" s="9"/>
+      <c r="D179" s="4"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
@@ -9569,7 +9740,7 @@
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="9"/>
+      <c r="D180" s="4"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
@@ -9592,7 +9763,7 @@
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="9"/>
+      <c r="D181" s="4"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
@@ -9615,7 +9786,7 @@
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
-      <c r="D182" s="9"/>
+      <c r="D182" s="4"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
@@ -9638,7 +9809,7 @@
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
-      <c r="D183" s="9"/>
+      <c r="D183" s="4"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
@@ -9661,7 +9832,7 @@
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
-      <c r="D184" s="9"/>
+      <c r="D184" s="4"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
@@ -9684,7 +9855,7 @@
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="9"/>
+      <c r="D185" s="4"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
@@ -9707,7 +9878,7 @@
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="9"/>
+      <c r="D186" s="4"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
@@ -9730,7 +9901,7 @@
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
-      <c r="D187" s="9"/>
+      <c r="D187" s="4"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
@@ -9753,7 +9924,7 @@
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
-      <c r="D188" s="9"/>
+      <c r="D188" s="4"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
@@ -9776,7 +9947,7 @@
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="9"/>
+      <c r="D189" s="4"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
@@ -9799,7 +9970,7 @@
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="9"/>
+      <c r="D190" s="4"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
@@ -9822,7 +9993,7 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="9"/>
+      <c r="D191" s="4"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
@@ -9845,7 +10016,7 @@
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
-      <c r="D192" s="9"/>
+      <c r="D192" s="4"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
@@ -9868,7 +10039,7 @@
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
-      <c r="D193" s="9"/>
+      <c r="D193" s="4"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
@@ -9891,7 +10062,7 @@
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
-      <c r="D194" s="9"/>
+      <c r="D194" s="4"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
@@ -9914,7 +10085,7 @@
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
-      <c r="D195" s="9"/>
+      <c r="D195" s="4"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
@@ -9937,7 +10108,7 @@
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
-      <c r="D196" s="9"/>
+      <c r="D196" s="4"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
@@ -9960,7 +10131,7 @@
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
-      <c r="D197" s="9"/>
+      <c r="D197" s="4"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
@@ -9983,7 +10154,7 @@
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
-      <c r="D198" s="9"/>
+      <c r="D198" s="4"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
@@ -10006,7 +10177,7 @@
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
-      <c r="D199" s="9"/>
+      <c r="D199" s="4"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
@@ -10029,7 +10200,7 @@
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
-      <c r="D200" s="9"/>
+      <c r="D200" s="4"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
@@ -10052,7 +10223,7 @@
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
-      <c r="D201" s="9"/>
+      <c r="D201" s="4"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
@@ -10075,7 +10246,7 @@
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
-      <c r="D202" s="9"/>
+      <c r="D202" s="4"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
@@ -10098,7 +10269,7 @@
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
-      <c r="D203" s="9"/>
+      <c r="D203" s="4"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
@@ -10121,7 +10292,7 @@
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
-      <c r="D204" s="9"/>
+      <c r="D204" s="4"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
@@ -10144,7 +10315,7 @@
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
-      <c r="D205" s="9"/>
+      <c r="D205" s="4"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
@@ -10167,7 +10338,7 @@
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
-      <c r="D206" s="9"/>
+      <c r="D206" s="4"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
@@ -10966,6 +11137,20 @@
     <row r="984" ht="15.75" customHeight="1"/>
     <row r="985" ht="15.75" customHeight="1"/>
     <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
@@ -10989,19 +11174,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="19" t="s">
         <v>111</v>
       </c>
       <c r="F1" s="1"/>
@@ -11026,15 +11211,15 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="34" t="str">
+      <c r="C2" s="25" t="str">
         <f>TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2020-11-03_06-50</v>
+        <v>2024-03-19_23-17</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>114</v>
